--- a/docs/Npay_단건결제_연동 체크리스트.xlsx
+++ b/docs/Npay_단건결제_연동 체크리스트.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\주정은\2026년\체크리스트 현행화\26 상반기\최종본\외부용\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\delio-next\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69A204CB-9304-4489-BBF7-C69BADC23B8D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="44260" yWindow="1700" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="44265" yWindow="1695" windowWidth="28800" windowHeight="15375" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="검수정보" sheetId="2" r:id="rId1"/>
@@ -18,7 +17,7 @@
     <sheet name="결제화면" sheetId="4" r:id="rId3"/>
     <sheet name="결제로직 취약성" sheetId="5" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0" calcMode="manual"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -28,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="276">
   <si>
     <t>담당자</t>
   </si>
@@ -75,9 +74,6 @@
     <t>개발 담당자</t>
   </si>
   <si>
-    <t>홍길동 (e-mail : honggildng@naver.com)</t>
-  </si>
-  <si>
     <t>검수 담당자</t>
   </si>
   <si>
@@ -96,16 +92,10 @@
     <t>가맹점 정보</t>
   </si>
   <si>
-    <t>가맹점 명 (가맹점 ID)</t>
-  </si>
-  <si>
     <t>Npay에 가입한 가맹점 명과 발급 받은신 계정을 작성해주시면 됩니다.</t>
   </si>
   <si>
     <t>가맹점 검수 환경</t>
-  </si>
-  <si>
-    <t>개발환경(  ) / 운영환경( O )</t>
   </si>
   <si>
     <t>개발 환경 검수(선택) / 운영 환경 검수(필수)
@@ -116,9 +106,6 @@
     <t>검수 환경 제공 방식</t>
   </si>
   <si>
-    <t>IP / 계정(테스트 계정 제공 필요)</t>
-  </si>
-  <si>
     <t>운영 환경 검수 시 외부 사용자에게 Npay 결제수단이 노출되지 않는 방향으로 
 특정 IP or 특정 계정 중 택1 하시어 검수 환경 제공이 필요합니다.
 이때 특정 계정을 제공하실 경우 2개의 테스트 계정을 함께 기재해 주시기 바랍니다.</t>
@@ -127,17 +114,10 @@
     <t>테스트 상품</t>
   </si>
   <si>
-    <t>상품 URL</t>
-  </si>
-  <si>
     <t>결제 테스트 가능한 상품이 있다면 URL 전달 바랍니다.</t>
   </si>
   <si>
     <t>결제 취소 제공</t>
-  </si>
-  <si>
-    <t>ex. 사용자 전체취소 가능
-관리자 전체,부분취소 가능</t>
   </si>
   <si>
     <t>가맹점의 취소 정책에 맞춰 테스트를 진행합니다.
@@ -147,17 +127,11 @@
     <t>주문 처리 지원</t>
   </si>
   <si>
-    <t>ex. 오전 10시 ~ 오후 7시 까지 지원 가능</t>
-  </si>
-  <si>
     <t>가맹점의 주문내역 처리 가능한 시간대 공유 바랍니다. 
 결제 취소 등 필요할 경우에 요청 드릴 예정입니다.</t>
   </si>
   <si>
     <t>과/면세 기준</t>
-  </si>
-  <si>
-    <t>과세 / 면세 / 과면세 복합</t>
   </si>
   <si>
     <t>가맹점 상품 유형의 과/면세 기준을 작성해 주시면 됩니다.
@@ -169,26 +143,16 @@
     <t>정산 기준</t>
   </si>
   <si>
-    <t>결제일 / 이용완료일 / 거래완료일</t>
-  </si>
-  <si>
     <t>Npay와 협의된 정산 기준을 작성해 주시면 됩니다.</t>
   </si>
   <si>
     <t>포인트 적립 기준</t>
   </si>
   <si>
-    <t>결제일 기준 자동 적립 / 이용완료일 기준 적립
-거래 완료 API 적립 / 포인트 적립 대상 아님</t>
-  </si>
-  <si>
     <t>Npay와 협의된 포인트 적립 기준을 작성해 주시면 됩니다.</t>
   </si>
   <si>
     <t>현금영수증 발행</t>
-  </si>
-  <si>
-    <t>가맹점 자체 발급 / Npay 발급 대행</t>
   </si>
   <si>
     <t>Npay 발급 대행을 원하실 경우 Npay와 사전 협의가 필요합니다.
@@ -211,33 +175,15 @@
     <t>PC Web</t>
   </si>
   <si>
-    <t>O / X</t>
-  </si>
-  <si>
-    <t>ex. http://www.naver.com/</t>
-  </si>
-  <si>
-    <t>ex. 크롬, 사파리, 파이어폭스 등</t>
-  </si>
-  <si>
     <t>Mobile Web</t>
   </si>
   <si>
-    <t>ex. http://m.naver.com/</t>
-  </si>
-  <si>
     <t>ex. 안드로이드 10 이상 , iOS 15 이상</t>
   </si>
   <si>
     <t>Mobile App</t>
   </si>
   <si>
-    <t>O / X
-O-1) WebView를 이용하여 웹 페이지를 로딩하는 구조
-O-2) Android 앱과 iOS 앱이 같은 API를 사용하는 구조
-X) App 없음</t>
-  </si>
-  <si>
     <t xml:space="preserve">ex. ipa, apk 설치 경로 또는 URL </t>
   </si>
   <si>
@@ -262,22 +208,13 @@
     <t>필수</t>
   </si>
   <si>
-    <t>ex. 주문서 페이지 Npay 결제하기 시</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
     <t>결제 승인 API</t>
   </si>
   <si>
-    <t>ex. 자체주문 생성 후 정상 주문 건에 한해 결제승인 요청 시</t>
-  </si>
-  <si>
     <t>결제 취소 API</t>
-  </si>
-  <si>
-    <t>ex. 주문생성 실패 시 / 고객 주문취소 시 / 관리자 주문취소 시</t>
   </si>
   <si>
     <t>부분필수</t>
@@ -334,9 +271,6 @@
     <t>결제창 오픈 방식</t>
   </si>
   <si>
-    <t>PC - page( O ) / popup(  )</t>
-  </si>
-  <si>
     <t>Open Type을 명시하지 않을 경우 page로 적용됩니다.</t>
   </si>
   <si>
@@ -353,28 +287,6 @@
   </si>
   <si>
     <t>productItems</t>
-  </si>
-  <si>
-    <t>ex. 아래 예시와 같이 가맹점 샘플 코드 입력 부탁드립니다.
-"productItems": [{
-"categoryType": "BOOK",
-"categoryId": "GENERAL",
-"uid": "107922211",
-"name": "한국사",
-"count": 10
-}, {
-"categoryType": "MUSIC",
-"categoryId": "CD",
-"uid": "299911002",
-"name": "러블리즈",
-"count": 1
-}]</t>
-  </si>
-  <si>
-    <t>결제 상품에 대한 상품 상세 정보(productItems) 전달은 필수 항목입니다.
-categoryType, categoryId, uid, name, count 는 공통 필수 전달 항목이며,
-그 외 parameter는 결제 상품 유형에 따라 필수 or 선택 항목입니다.
-자세한 내용은 [Npay 개발자센터]를 통해 확인 바랍니다.</t>
   </si>
   <si>
     <t>▶ 사전준비 항목</t>
@@ -499,30 +411,18 @@
     <t>네이버 페이지 이동 허용</t>
   </si>
   <si>
-    <t>Npay 사용을 위해 *.naver.com 도메인 페이지 이동 허용 필요</t>
-  </si>
-  <si>
     <t>네이버 쿠키 허용</t>
   </si>
   <si>
-    <t>네이버 로그인을 위해 네이버에서 발급하는 쿠키가 만료되지 않도록 설정 필요</t>
-  </si>
-  <si>
     <t>[네이버 앱 로그인] 허용</t>
   </si>
   <si>
-    <t>[네이버 앱 로그인] 사용을 위해 가맹점 앱 Webview scheme 허용 필요</t>
-  </si>
-  <si>
     <t>가맹점 주문생성</t>
   </si>
   <si>
     <t>결제 및 주문생성 체크</t>
   </si>
   <si>
-    <t>Npay · 가맹점 주문 체크를 진행하여 주문 누락이 발생되지 않도록 확인 필요</t>
-  </si>
-  <si>
     <t>필수</t>
   </si>
   <si>
@@ -532,29 +432,16 @@
     <t>Timeout 설정</t>
   </si>
   <si>
-    <t xml:space="preserve">※ 결제 승인 / 결제 취소 API: 60초
-※ 결제 내역 조회 / 현금영수증 금액 조회 / 거래 완료 / 포인트 적립 요청 API: 10초 </t>
-  </si>
-  <si>
     <t>결제 취소 실패</t>
   </si>
   <si>
     <t>결제 취소 API 응답 결과 체크</t>
   </si>
   <si>
-    <t>결제취소 API 요청에 대한 정상 처리 여부 확인 필요
-응답 코드 중 CancelNotComplete는 Npay 취소 진행 중 상태로 
-빠른 시일 내에 자동 취소될 예정이므로 가맹점에서는 취소 성공으로 처리 필요</t>
-  </si>
-  <si>
     <t>API 공통</t>
   </si>
   <si>
     <t>Npay 하위 호환성 기준 확인</t>
-  </si>
-  <si>
-    <t>Npay API 버전 변경 정책 및 변경 기준을 이해하고, 
-사용 및 운영에 문제가 없도록 처리 필요</t>
   </si>
   <si>
     <t>■ 단건결제 API 체크리스트</t>
@@ -809,10 +696,6 @@
 (검색 기간을 사용하는 경우 1일 단위 권장)</t>
   </si>
   <si>
-    <t>collectChainGroup는 필요시 그룹형 마스터 계정만 연동 되어있는지 확인
-(해당 계정을 마스터로 두는 모든 하위 계정의 결제내역을 조회할 수 있음)</t>
-  </si>
-  <si>
     <t>paymentIds를 정상적으로 전달하는지 확인
 (결제번호 리스트는 String[] 타입으로 연동 필요)</t>
   </si>
@@ -979,53 +862,361 @@
   </si>
   <si>
     <t>결제창 호출</t>
-    <phoneticPr fontId="21" type="noConversion"/>
+    <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
     <t>팝업 사이즈 확인 (툴바 포함 가로: 569px / 세로: 최소 920px)</t>
-    <phoneticPr fontId="21" type="noConversion"/>
+    <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
     <t>returnUrl 값에 가맹점 개인정보 데이터가 제외되었는지 확인
 (결제정보 외에 개인정보를 제 3자에게 제공시 정보통신망 법률상 약관동의가 필요)</t>
-    <phoneticPr fontId="21" type="noConversion"/>
+    <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
     <t>cancelReason 개인정보 데이터를 제외 후 전달하는지 확인
 취소사유는 서비스 오픈 후 고객 문의 대응 시 활용하며, 256바이트 미만 전달 필요</t>
-    <phoneticPr fontId="21" type="noConversion"/>
+    <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
     <t>Npay API 요청 파라미터에 이름, 생년월일, 연락처 등 개인정보 데이터가 제외되었는지 확인
 (특히 cancelReason, merchantExtraParameter 등 자유 입력 필드에 개인정보를 기재하는 경우 개인정보보호법 위반에 해당 됨)</t>
-    <phoneticPr fontId="21" type="noConversion"/>
+    <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
     <t>merchantUserKey 개인정보 데이터가 제외되었는지 확인
 (가맹점에서 구분할 수 있는 사용자 고유의 값으로 연동해야 함)</t>
-    <phoneticPr fontId="21" type="noConversion"/>
-  </si>
-  <si>
-    <t>Npay 환경별로 발급된 가맹점 인증정보를 구분하여 연동 필요</t>
-    <phoneticPr fontId="21" type="noConversion"/>
+    <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
     <t>가맹점 인증정보</t>
-    <phoneticPr fontId="21" type="noConversion"/>
+    <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
     <t>개인정보 보호</t>
-    <phoneticPr fontId="21" type="noConversion"/>
-  </si>
-  <si>
-    <t>Npay API 요청 파라미터에 개인정보가 제외되었는지 확인 필요</t>
-    <phoneticPr fontId="21" type="noConversion"/>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>서원준(hnk1203@naver.com)</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>서원준(hnk1203@naver.com)</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>델리오 (np_gxllc799187)</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>개발환경(  ) / 운영환경( O )</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">naverpay.review@delio.co.kr / Delionpay!2026
+naverpay1.review@delio.co.kr / Delionpay!2026
+</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.delio.co.kr — 위 테스트 계정으로 로그인 후 아무 상품이나 장바구니에 담아 결제하면 네이버페이 결제 테스트 가능
+</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용자 전체취소 가능 / 관리자 전체·부분취소 가능</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>평일 09:00 ~ 18:00</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>면세 (신선 과일=농산물 부가세 면세)</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>결제일 + 차주 목요일</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>결제일 + 15일 자동적립</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>Npay 발급 대행</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>o</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>x</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.delio.co.kr</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.delio.co.kr (반응형)</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>크롬, 사파리, 엣지</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>안드로이드 10 이상 / iOS 15 이상</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>O</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>O</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>O</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>X</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>X</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>주문서(결제) 페이지 네이버페이 결제 시</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>결제 완료 후 서버 검증(웹훅) 시 — 포트원 경유</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>주문생성 실패(재고 부족 등) 시 자동취소 / 고객 주문취소 / 관리자 취소·환불 시 — 모두 포트원 경유</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>PC - page(  ) / popup( O )</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>필수</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>결제 상품에 대한 상품 상세 정보(productItems) 전달은 필수 항목입니다.
+categoryType, categoryId, uid, name, count 는 공통 필수 전달 항목이며,
+그 외 parameter는 결제 상품 유형에 따라 필수 or 선택 항목입니다.
+자세한 내용은 [Npay 개발자센터]를 통해 확인 바랍니다.</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>O 
+(포트원 products 파라미터로 전달)</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>정상</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>정상</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>해당 사항 없음</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>해당 사항 없음</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>해당 사항 없음</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>정상</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>Npay 사용을 위해 *.naver.com 도메인 페이지 이동 허용 필요
+-모바일 웹 없음</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>네이버 로그인을 위해 네이버에서 발급하는 쿠키가 만료되지 않도록 설정 필요
+-모바일 웹 없음</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>[네이버 앱 로그인] 사용을 위해 가맹점 앱 Webview scheme 허용 필요
+-모바일 웹 없음</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>Npay · 가맹점 주문 체크를 진행하여 주문 누락이 발생되지 않도록 확인 필요
+결제 전 주문데이터 서버 저장(prepare)+웹훅 확정으로 주문 누락 방지 (카드·카카오로 검증됨)</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>※ 결제 승인 / 결제 취소 API: 60초
+※ 결제 내역 조회 / 현금영수증 금액 조회 / 거래 완료 / 포인트 적립 요청 API: 10초 
+포트원 경유 연동 완료 · 실결제 검증은 검수 오픈 후 진행 예정</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>결제취소 API 요청에 대한 정상 처리 여부 확인 필요
+응답 코드 중 CancelNotComplete는 Npay 취소 진행 중 상태로 
+빠른 시일 내에 자동 취소될 예정이므로 가맹점에서는 취소 성공으로 처리 필요
+-포트원 경유 연동 완료 · 실결제(취소) 검증은 검수 오픈 후 진행 예정</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>Npay API 버전 변경 정책 및 변경 기준을 이해하고, 
+사용 및 운영에 문제가 없도록 처리 필요
+-네이버 API 버전은 포트원 채널이 관리 · 검수 시 최종 확인</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>Npay 환경별로 발급된 가맹점 인증정보를 구분하여 연동 필요
+-운영환경 인증정보(Client ID·Secret·Chain ID) 포트원 채널 등록 완료</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>Npay API 요청 파라미터에 개인정보가 제외되었는지 확인 필요
+-취소사유 등 자유입력 필드에 개인정보 미기재. 결제자 정보는 PG(포트원)에 표준 전달</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>해당 사항 없음</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>정상</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>정상</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>collectChainGroup는 필요시 그룹형 마스터 계정만 연동 되어있는지 확인
+(해당 계정을 마스터로 두는 모든 하위 계정의 결제내역을 조회할 수 있음)</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>PC 팝업, 모바일 페이지 방식(iframe  미사용)</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>포트원이 네이버 규격 팝업 생성 (검수시 확인필요),네이버 이용정지(검수 전)로 결제창을 띄울 수 없어 확인 불가. 검수 오픈 후 확인 예정</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>네이버 이용정지(검수 전)로 결제창을 띄울 수 없어 확인 불가. 검수 오픈 후 확인 예정</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>포트원 경유 연동 · 네이버 이용정지로 실결제 미검증(검수 오픈 후 확인) / 모바일앱 미지원</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>자유입력 필드에 개인정보 미포함(코드 확인) · 포트원 경유 / 모바일앱 미지원</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>포트원 경유 연동 · 네이버 이용정지로 실결제 미검증(검수 오픈 후 확인) / 모바일앱 미지원</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>포트원 경유 연동 · 네이버 이용정지로 실결제 미검증(검수 오픈 후 확인) / 모바일앱 미지원</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>returnUrl에 개인정보 미포함 · 포트원 경유 / 모바일앱 미지원</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>포트원 경유 · 델리오 면세(과일) 처리 검수 시 확인 / 모바일앱 미지원</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용자키(merchantUserKey)에 개인정보 미포함(포트원 생성) / 모바일앱 미지원</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>취소사유에 개인정보 미포함(코드 확인) · 포트원 경유 / 모바일앱 미지원</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>포트원 경유 · 델리오 면세(과일) 처리 검수 시 확인 / 모바일앱 미지원</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>포트원 경유 연동 · 네이버 이용정지로 실결제 미검증(검수 오픈 후 확인) / 모바일앱 미지원</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>CancelNotComplete는 취소성공 처리(포트원) · 이용정지로 실검증은 검수 시 / 모바일앱 미지원</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>포트원 대시보드로 조회, 해당 API 직접 미연동</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>델리오 미사용(포트원 경유, 결제일 정산·자동적립)</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>정상</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>정상</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>해당 사항 없음</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>정상</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>실패·취소 시 PG 메시지(resultMessage) alert 표시 — 코드 확인됨 / 모바일앱 미지원</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>승인 실패 시 사유 메시지 alert 표시 — 코드 확인됨 / 모바일앱 미지원</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>네이버 결제화면 영역 · 이용정지로 확인 불가, 검수 오픈 후 확인</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>모바일 앱 없음(웹 전용)</t>
+  </si>
+  <si>
+    <t>표기 '네이버페이'(올바른 공식 표기), 잘못된 표기 없음 / 모바일앱 미지원</t>
+    <phoneticPr fontId="20" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1129,13 +1320,6 @@
       <charset val="129"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FFBFBFBF"/>
-      <name val="나눔고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <color theme="4"/>
@@ -1186,6 +1370,14 @@
       <name val="Arial"/>
       <family val="3"/>
       <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1240,7 +1432,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="57">
+  <borders count="55">
     <border>
       <left/>
       <right/>
@@ -1607,21 +1799,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thick">
-        <color theme="3" tint="0.39991454817346722"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thick">
-        <color theme="3" tint="0.39991454817346722"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thick">
         <color theme="3" tint="0.39991454817346722"/>
       </left>
@@ -1831,21 +2008,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thick">
-        <color theme="3" tint="0.39991454817346722"/>
-      </right>
-      <top style="thick">
-        <color theme="3" tint="0.39991454817346722"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thick">
         <color theme="3" tint="0.39991454817346722"/>
       </left>
@@ -1868,36 +2030,6 @@
       <top/>
       <bottom style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color theme="3" tint="0.39991454817346722"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color theme="3" tint="0.39991454817346722"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thick">
-        <color theme="3" tint="0.39991454817346722"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2028,8 +2160,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color theme="3" tint="0.39991454817346722"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color theme="3" tint="0.39991454817346722"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color theme="3" tint="0.39991454817346722"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2039,8 +2199,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="189">
+  <cellXfs count="182">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2074,12 +2237,6 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2101,65 +2258,14 @@
     <xf numFmtId="0" fontId="10" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2170,12 +2276,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2198,28 +2298,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2233,19 +2318,13 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2260,109 +2339,43 @@
     <xf numFmtId="0" fontId="10" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2371,25 +2384,25 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2404,9 +2417,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2416,34 +2426,166 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="21" xfId="3" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2452,7 +2594,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2467,7 +2609,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2497,13 +2639,13 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2512,7 +2654,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2609,10 +2751,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="보통 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+  <cellStyles count="4">
+    <cellStyle name="보통 2" xfId="1"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="표준 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="표준 2" xfId="2"/>
+    <cellStyle name="하이퍼링크" xfId="3" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2849,24 +2992,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:L68"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.75" style="1" customWidth="1"/>
-    <col min="2" max="2" width="41.58203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="41.625" style="1" customWidth="1"/>
     <col min="3" max="3" width="25.75" style="1" customWidth="1"/>
-    <col min="4" max="4" width="71.08203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="71.125" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.5" style="1" customWidth="1"/>
     <col min="6" max="11" width="9" style="1"/>
     <col min="12" max="12" width="15" style="1" customWidth="1"/>
     <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" s="2" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
@@ -2874,7 +3017,7 @@
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
     </row>
-    <row r="2" spans="1:4" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" s="2" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -2882,7 +3025,7 @@
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
     </row>
-    <row r="3" spans="1:4" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -2890,13 +3033,13 @@
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
     </row>
-    <row r="4" spans="1:4" ht="10.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="10.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>0</v>
       </c>
@@ -2904,725 +3047,744 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="75" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="10" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="10" t="s">
+      <c r="B8" s="76" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="11"/>
+      <c r="B9" s="12"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="15" t="s">
+      <c r="B11" s="14"/>
+    </row>
+    <row r="12" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="16"/>
-    </row>
-    <row r="12" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="17" t="s">
+      <c r="B12" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="C12" s="155" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="162" t="s">
+      <c r="D12" s="155"/>
+    </row>
+    <row r="13" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="162"/>
-    </row>
-    <row r="13" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="19" t="s">
+      <c r="B13" s="77" t="s">
+        <v>204</v>
+      </c>
+      <c r="C13" s="151" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="D13" s="152"/>
+    </row>
+    <row r="14" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="158" t="s">
+      <c r="B14" s="78" t="s">
+        <v>205</v>
+      </c>
+      <c r="C14" s="156" t="s">
         <v>15</v>
       </c>
-      <c r="D13" s="159"/>
-    </row>
-    <row r="14" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="19" t="s">
+      <c r="D14" s="157"/>
+    </row>
+    <row r="15" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B15" s="79" t="s">
+        <v>206</v>
+      </c>
+      <c r="C15" s="158" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="163" t="s">
+      <c r="D15" s="159"/>
+    </row>
+    <row r="16" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+      <c r="A16" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="164"/>
-    </row>
-    <row r="15" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="22" t="s">
+      <c r="B16" s="79" t="s">
+        <v>207</v>
+      </c>
+      <c r="C16" s="151" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="21" t="s">
+      <c r="D16" s="152"/>
+    </row>
+    <row r="17" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="165" t="s">
+      <c r="B17" s="80" t="s">
+        <v>208</v>
+      </c>
+      <c r="C17" s="151" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="166"/>
-    </row>
-    <row r="16" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="19" t="s">
+      <c r="D17" s="152"/>
+    </row>
+    <row r="18" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="21" t="s">
+      <c r="B18" s="81" t="s">
+        <v>209</v>
+      </c>
+      <c r="C18" s="153" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="158" t="s">
+      <c r="D18" s="154"/>
+    </row>
+    <row r="19" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="159"/>
-    </row>
-    <row r="17" spans="1:12" ht="40" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="19" t="s">
+      <c r="B19" s="82" t="s">
+        <v>210</v>
+      </c>
+      <c r="C19" s="140" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="23" t="s">
+      <c r="D19" s="141"/>
+    </row>
+    <row r="20" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="158" t="s">
+      <c r="B20" s="83" t="s">
+        <v>211</v>
+      </c>
+      <c r="C20" s="140" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="159"/>
-    </row>
-    <row r="18" spans="1:12" ht="40" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="22" t="s">
+      <c r="D20" s="141"/>
+    </row>
+    <row r="21" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="24" t="s">
+      <c r="B21" s="84" t="s">
+        <v>212</v>
+      </c>
+      <c r="C21" s="140" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="160" t="s">
+      <c r="D21" s="141"/>
+    </row>
+    <row r="22" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="161"/>
-    </row>
-    <row r="19" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="25" t="s">
+      <c r="B22" s="85" t="s">
+        <v>213</v>
+      </c>
+      <c r="C22" s="140" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="26" t="s">
+      <c r="D22" s="141"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A23" s="11"/>
+      <c r="B23" s="33"/>
+    </row>
+    <row r="25" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="147" t="s">
+      <c r="B25" s="74" t="s">
         <v>33</v>
       </c>
-      <c r="D19" s="148"/>
-    </row>
-    <row r="20" spans="1:12" ht="40" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="10" t="s">
+      <c r="C25" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B20" s="27" t="s">
+      <c r="D25" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="147" t="s">
+      <c r="E25" s="20"/>
+    </row>
+    <row r="26" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="D20" s="148"/>
-    </row>
-    <row r="21" spans="1:12" ht="40" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="10" t="s">
+      <c r="B26" s="86" t="s">
+        <v>214</v>
+      </c>
+      <c r="C26" s="88" t="s">
+        <v>216</v>
+      </c>
+      <c r="D26" s="91" t="s">
+        <v>218</v>
+      </c>
+      <c r="E26" s="20"/>
+    </row>
+    <row r="27" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="28" t="s">
+      <c r="B27" s="59" t="s">
+        <v>214</v>
+      </c>
+      <c r="C27" s="89" t="s">
+        <v>217</v>
+      </c>
+      <c r="D27" s="92" t="s">
+        <v>219</v>
+      </c>
+      <c r="E27" s="20"/>
+    </row>
+    <row r="28" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="87" t="s">
+        <v>215</v>
+      </c>
+      <c r="C28" s="90" t="s">
+        <v>40</v>
+      </c>
+      <c r="D28" s="93" t="s">
         <v>38</v>
       </c>
-      <c r="C21" s="147" t="s">
-        <v>39</v>
-      </c>
-      <c r="D21" s="148"/>
-    </row>
-    <row r="22" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="B22" s="29" t="s">
+      <c r="E28" s="20"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A31" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="147" t="s">
+    </row>
+    <row r="32" spans="1:12" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D22" s="148"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-    </row>
-    <row r="25" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="8" t="s">
+      <c r="B32" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="C32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="D32" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="D25" s="9" t="s">
+      <c r="E32" s="142" t="s">
         <v>46</v>
       </c>
-      <c r="E25" s="30"/>
-    </row>
-    <row r="26" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="10" t="s">
+      <c r="F32" s="143"/>
+      <c r="G32" s="143"/>
+      <c r="H32" s="143"/>
+      <c r="I32" s="143"/>
+      <c r="J32" s="143"/>
+      <c r="K32" s="143"/>
+      <c r="L32" s="144"/>
+    </row>
+    <row r="33" spans="1:12" ht="20.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="B26" s="31" t="s">
+      <c r="B33" s="68" t="s">
+        <v>194</v>
+      </c>
+      <c r="C33" s="94" t="s">
+        <v>220</v>
+      </c>
+      <c r="D33" s="96" t="s">
+        <v>225</v>
+      </c>
+      <c r="E33" s="145" t="s">
         <v>48</v>
       </c>
-      <c r="C26" s="32" t="s">
+      <c r="F33" s="146"/>
+      <c r="G33" s="146"/>
+      <c r="H33" s="146"/>
+      <c r="I33" s="146"/>
+      <c r="J33" s="146"/>
+      <c r="K33" s="146"/>
+      <c r="L33" s="141"/>
+    </row>
+    <row r="34" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="B34" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="D26" s="33" t="s">
+      <c r="C34" s="59" t="s">
+        <v>221</v>
+      </c>
+      <c r="D34" s="46" t="s">
+        <v>226</v>
+      </c>
+      <c r="E34" s="147" t="s">
+        <v>48</v>
+      </c>
+      <c r="F34" s="148"/>
+      <c r="G34" s="148"/>
+      <c r="H34" s="148"/>
+      <c r="I34" s="148"/>
+      <c r="J34" s="148"/>
+      <c r="K34" s="148"/>
+      <c r="L34" s="149"/>
+    </row>
+    <row r="35" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="B35" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="E26" s="30"/>
-    </row>
-    <row r="27" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="10" t="s">
+      <c r="C35" s="59" t="s">
+        <v>222</v>
+      </c>
+      <c r="D35" s="97" t="s">
+        <v>227</v>
+      </c>
+      <c r="E35" s="150" t="s">
+        <v>48</v>
+      </c>
+      <c r="F35" s="136"/>
+      <c r="G35" s="136"/>
+      <c r="H35" s="136"/>
+      <c r="I35" s="136"/>
+      <c r="J35" s="136"/>
+      <c r="K35" s="136"/>
+      <c r="L35" s="137"/>
+    </row>
+    <row r="36" spans="1:12" ht="75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="B27" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="C27" s="35" t="s">
+      <c r="B36" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="D27" s="36" t="s">
+      <c r="C36" s="59" t="s">
+        <v>223</v>
+      </c>
+      <c r="D36" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="E27" s="30"/>
-    </row>
-    <row r="28" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="10" t="s">
+      <c r="E36" s="130" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="37" t="s">
+      <c r="F36" s="131"/>
+      <c r="G36" s="131"/>
+      <c r="H36" s="131"/>
+      <c r="I36" s="131"/>
+      <c r="J36" s="131"/>
+      <c r="K36" s="131"/>
+      <c r="L36" s="132"/>
+    </row>
+    <row r="37" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="B37" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="38" t="s">
+      <c r="C37" s="59" t="s">
+        <v>223</v>
+      </c>
+      <c r="D37" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="D28" s="39" t="s">
-        <v>53</v>
-      </c>
-      <c r="E28" s="30"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="40" t="s">
+      <c r="E37" s="130" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="32" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="8" t="s">
+      <c r="F37" s="133"/>
+      <c r="G37" s="133"/>
+      <c r="H37" s="133"/>
+      <c r="I37" s="133"/>
+      <c r="J37" s="133"/>
+      <c r="K37" s="133"/>
+      <c r="L37" s="134"/>
+    </row>
+    <row r="38" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B38" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="C38" s="59" t="s">
+        <v>224</v>
+      </c>
+      <c r="D38" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="D32" s="9" t="s">
+      <c r="E38" s="135" t="s">
         <v>61</v>
       </c>
-      <c r="E32" s="149" t="s">
+      <c r="F38" s="136"/>
+      <c r="G38" s="136"/>
+      <c r="H38" s="136"/>
+      <c r="I38" s="136"/>
+      <c r="J38" s="136"/>
+      <c r="K38" s="136"/>
+      <c r="L38" s="137"/>
+    </row>
+    <row r="39" spans="1:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="B39" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="F32" s="150"/>
-      <c r="G32" s="150"/>
-      <c r="H32" s="150"/>
-      <c r="I32" s="150"/>
-      <c r="J32" s="150"/>
-      <c r="K32" s="150"/>
-      <c r="L32" s="151"/>
-    </row>
-    <row r="33" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="42" t="s">
+      <c r="C39" s="95" t="s">
+        <v>223</v>
+      </c>
+      <c r="D39" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="E39" s="135" t="s">
         <v>63</v>
       </c>
-      <c r="B33" s="118" t="s">
-        <v>224</v>
-      </c>
-      <c r="C33" s="43" t="s">
-        <v>48</v>
-      </c>
-      <c r="D33" s="44" t="s">
+      <c r="F39" s="138"/>
+      <c r="G39" s="138"/>
+      <c r="H39" s="138"/>
+      <c r="I39" s="138"/>
+      <c r="J39" s="138"/>
+      <c r="K39" s="138"/>
+      <c r="L39" s="139"/>
+    </row>
+    <row r="40" spans="1:12" ht="13.5" thickTop="1" x14ac:dyDescent="0.2"/>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A42" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="E33" s="152" t="s">
+    </row>
+    <row r="43" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B43" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="F33" s="153"/>
-      <c r="G33" s="153"/>
-      <c r="H33" s="153"/>
-      <c r="I33" s="153"/>
-      <c r="J33" s="153"/>
-      <c r="K33" s="153"/>
-      <c r="L33" s="148"/>
-    </row>
-    <row r="34" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="45" t="s">
-        <v>63</v>
-      </c>
-      <c r="B34" s="46" t="s">
+      <c r="C43" s="125" t="s">
+        <v>46</v>
+      </c>
+      <c r="D43" s="127"/>
+    </row>
+    <row r="44" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="119" t="s">
         <v>66</v>
       </c>
-      <c r="C34" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="D34" s="47" t="s">
+      <c r="B44" s="98" t="s">
+        <v>228</v>
+      </c>
+      <c r="C44" s="121" t="s">
         <v>67</v>
       </c>
-      <c r="E34" s="154" t="s">
-        <v>65</v>
-      </c>
-      <c r="F34" s="155"/>
-      <c r="G34" s="155"/>
-      <c r="H34" s="155"/>
-      <c r="I34" s="155"/>
-      <c r="J34" s="155"/>
-      <c r="K34" s="155"/>
-      <c r="L34" s="156"/>
-    </row>
-    <row r="35" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="45" t="s">
-        <v>63</v>
-      </c>
-      <c r="B35" s="46" t="s">
+      <c r="D44" s="122"/>
+    </row>
+    <row r="45" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="120"/>
+      <c r="B45" s="99" t="s">
         <v>68</v>
       </c>
-      <c r="C35" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="D35" s="47" t="s">
+      <c r="C45" s="123"/>
+      <c r="D45" s="124"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A46" s="11"/>
+      <c r="B46" s="32"/>
+      <c r="C46" s="33"/>
+      <c r="D46" s="33"/>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A47" s="21"/>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A48" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="E35" s="157" t="s">
-        <v>65</v>
-      </c>
-      <c r="F35" s="143"/>
-      <c r="G35" s="143"/>
-      <c r="H35" s="143"/>
-      <c r="I35" s="143"/>
-      <c r="J35" s="143"/>
-      <c r="K35" s="143"/>
-      <c r="L35" s="144"/>
-    </row>
-    <row r="36" spans="1:12" ht="75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="45" t="s">
+    </row>
+    <row r="49" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B49" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="B36" s="48" t="s">
+      <c r="C49" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D49" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C36" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="D36" s="49" t="s">
+      <c r="E49" s="125" t="s">
+        <v>46</v>
+      </c>
+      <c r="F49" s="126"/>
+      <c r="G49" s="126"/>
+      <c r="H49" s="126"/>
+      <c r="I49" s="126"/>
+      <c r="J49" s="126"/>
+      <c r="K49" s="126"/>
+      <c r="L49" s="127"/>
+    </row>
+    <row r="50" spans="1:12" ht="206.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="24" t="s">
+        <v>229</v>
+      </c>
+      <c r="B50" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E36" s="137" t="s">
+      <c r="C50" s="101" t="s">
+        <v>231</v>
+      </c>
+      <c r="D50" s="100"/>
+      <c r="E50" s="128" t="s">
+        <v>230</v>
+      </c>
+      <c r="F50" s="129"/>
+      <c r="G50" s="129"/>
+      <c r="H50" s="129"/>
+      <c r="I50" s="129"/>
+      <c r="J50" s="129"/>
+      <c r="K50" s="129"/>
+      <c r="L50" s="129"/>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A51" s="35"/>
+      <c r="B51" s="35"/>
+      <c r="C51" s="32"/>
+      <c r="D51" s="36"/>
+      <c r="E51" s="35"/>
+      <c r="F51" s="33"/>
+      <c r="G51" s="33"/>
+      <c r="H51" s="33"/>
+      <c r="I51" s="33"/>
+      <c r="J51" s="33"/>
+      <c r="K51" s="33"/>
+      <c r="L51" s="33"/>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A53" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="F36" s="138"/>
-      <c r="G36" s="138"/>
-      <c r="H36" s="138"/>
-      <c r="I36" s="138"/>
-      <c r="J36" s="138"/>
-      <c r="K36" s="138"/>
-      <c r="L36" s="139"/>
-    </row>
-    <row r="37" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="45" t="s">
-        <v>70</v>
-      </c>
-      <c r="B37" s="50" t="s">
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A54" s="37" t="s">
         <v>74</v>
       </c>
-      <c r="C37" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="D37" s="47" t="s">
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A55" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="E37" s="137" t="s">
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A56" s="37" t="s">
         <v>76</v>
       </c>
-      <c r="F37" s="140"/>
-      <c r="G37" s="140"/>
-      <c r="H37" s="140"/>
-      <c r="I37" s="140"/>
-      <c r="J37" s="140"/>
-      <c r="K37" s="140"/>
-      <c r="L37" s="141"/>
-    </row>
-    <row r="38" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="45" t="s">
+    </row>
+    <row r="57" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B57" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="B38" s="46" t="s">
+      <c r="C57" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="C38" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="D38" s="47" t="s">
+      <c r="D57" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="E38" s="142" t="s">
+      <c r="E57" s="38" t="s">
         <v>80</v>
       </c>
-      <c r="F38" s="143"/>
-      <c r="G38" s="143"/>
-      <c r="H38" s="143"/>
-      <c r="I38" s="143"/>
-      <c r="J38" s="143"/>
-      <c r="K38" s="143"/>
-      <c r="L38" s="144"/>
-    </row>
-    <row r="39" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="51" t="s">
-        <v>77</v>
-      </c>
-      <c r="B39" s="46" t="s">
+    </row>
+    <row r="58" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="39" t="s">
+        <v>47</v>
+      </c>
+      <c r="B58" s="39" t="s">
         <v>81</v>
       </c>
-      <c r="C39" s="52" t="s">
-        <v>48</v>
-      </c>
-      <c r="D39" s="53" t="s">
-        <v>75</v>
-      </c>
-      <c r="E39" s="142" t="s">
+      <c r="C58" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="F39" s="145"/>
-      <c r="G39" s="145"/>
-      <c r="H39" s="145"/>
-      <c r="I39" s="145"/>
-      <c r="J39" s="145"/>
-      <c r="K39" s="145"/>
-      <c r="L39" s="146"/>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A42" s="119" t="s">
+      <c r="D58" s="10" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="43" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B43" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="C43" s="132" t="s">
-        <v>62</v>
-      </c>
-      <c r="D43" s="134"/>
-    </row>
-    <row r="44" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="126" t="s">
+      <c r="E58" s="102" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="39" t="s">
+        <v>47</v>
+      </c>
+      <c r="B59" s="39" t="s">
         <v>85</v>
       </c>
-      <c r="B44" s="54" t="s">
+      <c r="C59" s="39" t="s">
         <v>86</v>
       </c>
-      <c r="C44" s="128" t="s">
+      <c r="D59" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="D44" s="129"/>
-    </row>
-    <row r="45" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="127"/>
-      <c r="B45" s="55" t="s">
+      <c r="E59" s="102" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="118" t="s">
+        <v>47</v>
+      </c>
+      <c r="B60" s="118" t="s">
         <v>88</v>
       </c>
-      <c r="C45" s="130"/>
-      <c r="D45" s="131"/>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A46" s="13"/>
-      <c r="B46" s="56"/>
-      <c r="C46" s="57"/>
-      <c r="D46" s="57"/>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A47" s="40"/>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A48" s="40" t="s">
+      <c r="C60" s="39" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="49" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B49" s="8" t="s">
+      <c r="D60" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="E60" s="102" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="118"/>
+      <c r="B61" s="118"/>
+      <c r="C61" s="39" t="s">
         <v>90</v>
       </c>
-      <c r="C49" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="D49" s="9" t="s">
+      <c r="D61" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="E61" s="102" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="118"/>
+      <c r="B62" s="118"/>
+      <c r="C62" s="39" t="s">
         <v>91</v>
       </c>
-      <c r="E49" s="132" t="s">
-        <v>62</v>
-      </c>
-      <c r="F49" s="133"/>
-      <c r="G49" s="133"/>
-      <c r="H49" s="133"/>
-      <c r="I49" s="133"/>
-      <c r="J49" s="133"/>
-      <c r="K49" s="133"/>
-      <c r="L49" s="134"/>
-    </row>
-    <row r="50" spans="1:12" ht="206.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="45" t="s">
-        <v>63</v>
-      </c>
-      <c r="B50" s="46" t="s">
+      <c r="D62" s="19" t="s">
+        <v>240</v>
+      </c>
+      <c r="E62" s="102" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="39" t="s">
+        <v>47</v>
+      </c>
+      <c r="B63" s="39" t="s">
         <v>92</v>
       </c>
-      <c r="C50" s="58" t="s">
-        <v>48</v>
-      </c>
-      <c r="D50" s="59" t="s">
+      <c r="C63" s="39" t="s">
         <v>93</v>
       </c>
-      <c r="E50" s="135" t="s">
+      <c r="D63" s="19" t="s">
+        <v>241</v>
+      </c>
+      <c r="E63" s="102" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A64" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="F50" s="136"/>
-      <c r="G50" s="136"/>
-      <c r="H50" s="136"/>
-      <c r="I50" s="136"/>
-      <c r="J50" s="136"/>
-      <c r="K50" s="136"/>
-      <c r="L50" s="136"/>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A51" s="61"/>
-      <c r="B51" s="61"/>
-      <c r="C51" s="56"/>
-      <c r="D51" s="62"/>
-      <c r="E51" s="61"/>
-      <c r="F51" s="57"/>
-      <c r="G51" s="57"/>
-      <c r="H51" s="57"/>
-      <c r="I51" s="57"/>
-      <c r="J51" s="57"/>
-      <c r="K51" s="57"/>
-      <c r="L51" s="57"/>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A53" s="40" t="s">
+      <c r="B64" s="39" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A54" s="63" t="s">
+      <c r="C64" s="39" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A55" s="63" t="s">
+      <c r="D64" s="19" t="s">
+        <v>242</v>
+      </c>
+      <c r="E64" s="102" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+      <c r="A65" s="39" t="s">
+        <v>94</v>
+      </c>
+      <c r="B65" s="39" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A56" s="63" t="s">
+      <c r="C65" s="39" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="57" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B57" s="8" t="s">
+      <c r="D65" s="19" t="s">
+        <v>243</v>
+      </c>
+      <c r="E65" s="102" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A66" s="118" t="s">
+        <v>94</v>
+      </c>
+      <c r="B66" s="118" t="s">
         <v>99</v>
       </c>
-      <c r="C57" s="8" t="s">
+      <c r="C66" s="39" t="s">
         <v>100</v>
       </c>
-      <c r="D57" s="41" t="s">
-        <v>101</v>
-      </c>
-      <c r="E57" s="64" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="65" t="s">
-        <v>63</v>
-      </c>
-      <c r="B58" s="65" t="s">
-        <v>103</v>
-      </c>
-      <c r="C58" s="65" t="s">
-        <v>104</v>
-      </c>
-      <c r="D58" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="E58" s="66" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="65" t="s">
-        <v>63</v>
-      </c>
-      <c r="B59" s="65" t="s">
-        <v>107</v>
-      </c>
-      <c r="C59" s="65" t="s">
-        <v>108</v>
-      </c>
-      <c r="D59" s="25" t="s">
-        <v>109</v>
-      </c>
-      <c r="E59" s="66"/>
-    </row>
-    <row r="60" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="125" t="s">
-        <v>63</v>
-      </c>
-      <c r="B60" s="125" t="s">
-        <v>110</v>
-      </c>
-      <c r="C60" s="65" t="s">
-        <v>111</v>
-      </c>
-      <c r="D60" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="E60" s="66"/>
-    </row>
-    <row r="61" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="125"/>
-      <c r="B61" s="125"/>
-      <c r="C61" s="65" t="s">
-        <v>113</v>
-      </c>
-      <c r="D61" s="25" t="s">
-        <v>114</v>
-      </c>
-      <c r="E61" s="66"/>
-    </row>
-    <row r="62" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="125"/>
-      <c r="B62" s="125"/>
-      <c r="C62" s="65" t="s">
-        <v>115</v>
-      </c>
-      <c r="D62" s="25" t="s">
-        <v>116</v>
-      </c>
-      <c r="E62" s="66"/>
-    </row>
-    <row r="63" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="65" t="s">
-        <v>63</v>
-      </c>
-      <c r="B63" s="65" t="s">
-        <v>117</v>
-      </c>
-      <c r="C63" s="65" t="s">
-        <v>118</v>
-      </c>
-      <c r="D63" s="25" t="s">
-        <v>119</v>
-      </c>
-      <c r="E63" s="66"/>
-    </row>
-    <row r="64" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="65" t="s">
-        <v>120</v>
-      </c>
-      <c r="B64" s="65" t="s">
-        <v>121</v>
-      </c>
-      <c r="C64" s="65" t="s">
-        <v>122</v>
-      </c>
-      <c r="D64" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="E64" s="66"/>
-    </row>
-    <row r="65" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="65" t="s">
-        <v>120</v>
-      </c>
-      <c r="B65" s="65" t="s">
-        <v>124</v>
-      </c>
-      <c r="C65" s="65" t="s">
-        <v>125</v>
-      </c>
-      <c r="D65" s="25" t="s">
-        <v>126</v>
-      </c>
-      <c r="E65" s="66"/>
-    </row>
-    <row r="66" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="125" t="s">
-        <v>120</v>
-      </c>
-      <c r="B66" s="125" t="s">
-        <v>127</v>
-      </c>
-      <c r="C66" s="65" t="s">
-        <v>128</v>
-      </c>
-      <c r="D66" s="25" t="s">
-        <v>129</v>
-      </c>
-      <c r="E66" s="66"/>
-    </row>
-    <row r="67" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="125"/>
-      <c r="B67" s="125"/>
-      <c r="C67" s="117" t="s">
-        <v>231</v>
-      </c>
-      <c r="D67" s="25" t="s">
-        <v>230</v>
-      </c>
-      <c r="E67" s="121"/>
-    </row>
-    <row r="68" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="125"/>
-      <c r="B68" s="125"/>
-      <c r="C68" s="122" t="s">
+      <c r="D66" s="19" t="s">
+        <v>244</v>
+      </c>
+      <c r="E66" s="102" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="118"/>
+      <c r="B67" s="118"/>
+      <c r="C67" s="67" t="s">
+        <v>200</v>
+      </c>
+      <c r="D67" s="19" t="s">
+        <v>245</v>
+      </c>
+      <c r="E67" s="103" t="s">
         <v>232</v>
       </c>
-      <c r="D68" s="123" t="s">
-        <v>233</v>
-      </c>
-      <c r="E68" s="67"/>
+    </row>
+    <row r="68" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="118"/>
+      <c r="B68" s="118"/>
+      <c r="C68" s="71" t="s">
+        <v>201</v>
+      </c>
+      <c r="D68" s="72" t="s">
+        <v>246</v>
+      </c>
+      <c r="E68" s="104" t="s">
+        <v>232</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="28">
@@ -3655,645 +3817,1072 @@
     <mergeCell ref="A60:A62"/>
     <mergeCell ref="B60:B62"/>
   </mergeCells>
-  <phoneticPr fontId="21" type="noConversion"/>
+  <phoneticPr fontId="20" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="C26" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:F61"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26" style="1" customWidth="1"/>
-    <col min="2" max="2" width="92.58203125" style="1" customWidth="1"/>
-    <col min="3" max="5" width="12.58203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="92.625" style="1" customWidth="1"/>
+    <col min="3" max="5" width="12.625" style="1" customWidth="1"/>
     <col min="6" max="6" width="64.5" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="68" t="s">
+    <row r="1" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="40" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="41" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="42" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="42" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="42" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="127" t="s">
+        <v>106</v>
+      </c>
+      <c r="B6" s="125" t="s">
+        <v>107</v>
+      </c>
+      <c r="C6" s="164" t="s">
+        <v>108</v>
+      </c>
+      <c r="D6" s="164"/>
+      <c r="E6" s="164"/>
+      <c r="F6" s="160" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="162"/>
+      <c r="B7" s="163"/>
+      <c r="C7" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="161"/>
+    </row>
+    <row r="8" spans="1:6" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="171" t="s">
+        <v>99</v>
+      </c>
+      <c r="B8" s="44" t="s">
+        <v>110</v>
+      </c>
+      <c r="C8" s="109" t="s">
+        <v>233</v>
+      </c>
+      <c r="D8" s="110" t="s">
+        <v>232</v>
+      </c>
+      <c r="E8" s="110" t="s">
+        <v>247</v>
+      </c>
+      <c r="F8" s="107" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="172"/>
+      <c r="B9" s="45" t="s">
+        <v>114</v>
+      </c>
+      <c r="C9" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D9" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E9" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F9" s="107" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="172"/>
+      <c r="B10" s="45" t="s">
+        <v>115</v>
+      </c>
+      <c r="C10" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D10" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E10" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F10" s="107" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="172"/>
+      <c r="B11" s="45" t="s">
+        <v>116</v>
+      </c>
+      <c r="C11" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D11" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E11" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F11" s="107" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="172"/>
+      <c r="B12" s="45" t="s">
+        <v>117</v>
+      </c>
+      <c r="C12" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D12" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E12" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F12" s="107" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="172"/>
+      <c r="B13" s="70" t="s">
+        <v>198</v>
+      </c>
+      <c r="C13" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D13" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E13" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F13" s="107" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="172"/>
+      <c r="B14" s="70" t="s">
+        <v>118</v>
+      </c>
+      <c r="C14" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D14" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E14" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F14" s="107" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="173"/>
+      <c r="B15" s="70" t="s">
+        <v>119</v>
+      </c>
+      <c r="C15" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D15" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E15" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F15" s="107" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="165" t="s">
+        <v>120</v>
+      </c>
+      <c r="B16" s="70" t="s">
+        <v>121</v>
+      </c>
+      <c r="C16" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D16" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E16" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F16" s="107" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="166"/>
+      <c r="B17" s="70" t="s">
+        <v>122</v>
+      </c>
+      <c r="C17" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D17" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E17" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F17" s="107" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="166"/>
+      <c r="B18" s="70" t="s">
+        <v>123</v>
+      </c>
+      <c r="C18" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D18" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E18" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F18" s="107" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="166"/>
+      <c r="B19" s="70" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D19" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E19" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F19" s="107" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="166"/>
+      <c r="B20" s="70" t="s">
+        <v>196</v>
+      </c>
+      <c r="C20" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D20" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E20" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F20" s="107" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="166"/>
+      <c r="B21" s="70" t="s">
+        <v>125</v>
+      </c>
+      <c r="C21" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D21" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E21" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F21" s="107" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="166"/>
+      <c r="B22" s="70" t="s">
+        <v>126</v>
+      </c>
+      <c r="C22" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D22" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E22" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F22" s="107" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="166"/>
+      <c r="B23" s="70" t="s">
+        <v>127</v>
+      </c>
+      <c r="C23" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D23" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E23" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F23" s="107" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="166"/>
+      <c r="B24" s="70" t="s">
+        <v>128</v>
+      </c>
+      <c r="C24" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D24" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E24" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F24" s="107" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="166"/>
+      <c r="B25" s="70" t="s">
+        <v>129</v>
+      </c>
+      <c r="C25" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D25" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E25" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F25" s="107" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="166"/>
+      <c r="B26" s="70" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="69" t="s">
+      <c r="C26" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D26" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E26" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F26" s="107" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="166"/>
+      <c r="B27" s="70" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="70" t="s">
+      <c r="C27" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D27" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E27" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F27" s="107" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="166"/>
+      <c r="B28" s="70" t="s">
+        <v>199</v>
+      </c>
+      <c r="C28" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D28" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E28" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F28" s="107" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="166"/>
+      <c r="B29" s="70" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="70" t="s">
+      <c r="C29" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D29" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E29" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F29" s="107" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="166"/>
+      <c r="B30" s="70" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="70" t="s">
+      <c r="C30" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D30" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E30" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F30" s="107" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="166"/>
+      <c r="B31" s="70" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="134" t="s">
+      <c r="C31" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D31" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E31" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F31" s="107" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="166"/>
+      <c r="B32" s="70" t="s">
         <v>135</v>
       </c>
-      <c r="B6" s="132" t="s">
+      <c r="C32" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D32" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E32" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F32" s="107" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="166"/>
+      <c r="B33" s="70" t="s">
         <v>136</v>
       </c>
-      <c r="C6" s="171" t="s">
+      <c r="C33" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D33" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E33" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F33" s="107" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="166"/>
+      <c r="B34" s="70" t="s">
         <v>137</v>
       </c>
-      <c r="D6" s="171"/>
-      <c r="E6" s="171"/>
-      <c r="F6" s="167" t="s">
+      <c r="C34" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D34" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E34" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F34" s="107" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="166"/>
+      <c r="B35" s="70" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="169"/>
-      <c r="B7" s="170"/>
-      <c r="C7" s="71" t="s">
-        <v>47</v>
-      </c>
-      <c r="D7" s="71" t="s">
-        <v>51</v>
-      </c>
-      <c r="E7" s="71" t="s">
-        <v>54</v>
-      </c>
-      <c r="F7" s="168"/>
-    </row>
-    <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="178" t="s">
-        <v>127</v>
-      </c>
-      <c r="B8" s="72" t="s">
+      <c r="C35" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D35" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E35" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F35" s="107" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="B36" s="73" t="s">
         <v>139</v>
       </c>
-      <c r="C8" s="73" t="s">
-        <v>106</v>
-      </c>
-      <c r="D8" s="74" t="s">
+      <c r="C36" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D36" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E36" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F36" s="107" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="177" t="s">
+        <v>50</v>
+      </c>
+      <c r="B37" s="70" t="s">
         <v>140</v>
       </c>
-      <c r="E8" s="74" t="s">
+      <c r="C37" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D37" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E37" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F37" s="107" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="178"/>
+      <c r="B38" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="F8" s="75" t="s">
+      <c r="C38" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D38" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E38" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F38" s="107" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="178"/>
+      <c r="B39" s="70" t="s">
+        <v>197</v>
+      </c>
+      <c r="C39" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D39" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E39" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F39" s="107" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="178"/>
+      <c r="B40" s="70" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="179"/>
-      <c r="B9" s="76" t="s">
+      <c r="C40" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D40" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E40" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F40" s="107" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="178"/>
+      <c r="B41" s="70" t="s">
+        <v>129</v>
+      </c>
+      <c r="C41" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D41" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E41" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F41" s="107" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="178"/>
+      <c r="B42" s="70" t="s">
+        <v>130</v>
+      </c>
+      <c r="C42" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D42" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E42" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F42" s="107" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="178"/>
+      <c r="B43" s="70" t="s">
         <v>143</v>
       </c>
-      <c r="C9" s="77"/>
-      <c r="D9" s="78"/>
-      <c r="E9" s="78"/>
-      <c r="F9" s="79"/>
-    </row>
-    <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="179"/>
-      <c r="B10" s="76" t="s">
+      <c r="C43" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D43" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E43" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F43" s="107" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="178"/>
+      <c r="B44" s="70" t="s">
         <v>144</v>
       </c>
-      <c r="C10" s="77"/>
-      <c r="D10" s="78"/>
-      <c r="E10" s="78"/>
-      <c r="F10" s="79"/>
-    </row>
-    <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="179"/>
-      <c r="B11" s="76" t="s">
+      <c r="C44" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D44" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E44" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F44" s="107" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="178"/>
+      <c r="B45" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="C11" s="77"/>
-      <c r="D11" s="78"/>
-      <c r="E11" s="78"/>
-      <c r="F11" s="79"/>
-    </row>
-    <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="179"/>
-      <c r="B12" s="76" t="s">
+      <c r="C45" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D45" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E45" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F45" s="107" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="178"/>
+      <c r="B46" s="70" t="s">
         <v>146</v>
       </c>
-      <c r="C12" s="77"/>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="79"/>
-    </row>
-    <row r="13" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="179"/>
-      <c r="B13" s="120" t="s">
-        <v>228</v>
-      </c>
-      <c r="C13" s="77"/>
-      <c r="D13" s="78"/>
-      <c r="E13" s="78"/>
-      <c r="F13" s="79"/>
-    </row>
-    <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="179"/>
-      <c r="B14" s="120" t="s">
+      <c r="C46" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D46" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E46" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F46" s="107" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="178"/>
+      <c r="B47" s="70" t="s">
         <v>147</v>
       </c>
-      <c r="C14" s="77"/>
-      <c r="D14" s="78"/>
-      <c r="E14" s="78"/>
-      <c r="F14" s="79"/>
-    </row>
-    <row r="15" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="180"/>
-      <c r="B15" s="120" t="s">
+      <c r="C47" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D47" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E47" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F47" s="107" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="178"/>
+      <c r="B48" s="70" t="s">
         <v>148</v>
       </c>
-      <c r="C15" s="77"/>
-      <c r="D15" s="78"/>
-      <c r="E15" s="78"/>
-      <c r="F15" s="79"/>
-    </row>
-    <row r="16" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="172" t="s">
+      <c r="C48" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D48" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E48" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F48" s="107" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="178"/>
+      <c r="B49" s="70" t="s">
         <v>149</v>
       </c>
-      <c r="B16" s="120" t="s">
+      <c r="C49" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D49" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E49" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F49" s="107" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="178"/>
+      <c r="B50" s="70" t="s">
         <v>150</v>
       </c>
-      <c r="C16" s="77"/>
-      <c r="D16" s="78"/>
-      <c r="E16" s="78"/>
-      <c r="F16" s="79"/>
-    </row>
-    <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="173"/>
-      <c r="B17" s="120" t="s">
+      <c r="C50" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D50" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E50" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F50" s="107" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="179"/>
+      <c r="B51" s="70" t="s">
         <v>151</v>
       </c>
-      <c r="C17" s="77"/>
-      <c r="D17" s="78"/>
-      <c r="E17" s="78"/>
-      <c r="F17" s="79"/>
-    </row>
-    <row r="18" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="173"/>
-      <c r="B18" s="120" t="s">
+      <c r="C51" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="D51" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E51" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F51" s="107" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="167" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" s="70" t="s">
         <v>152</v>
       </c>
-      <c r="C18" s="77"/>
-      <c r="D18" s="78"/>
-      <c r="E18" s="78"/>
-      <c r="F18" s="79"/>
-    </row>
-    <row r="19" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="173"/>
-      <c r="B19" s="120" t="s">
+      <c r="C52" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="D52" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="E52" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F52" s="107" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="168"/>
+      <c r="B53" s="70" t="s">
         <v>153</v>
       </c>
-      <c r="C19" s="77"/>
-      <c r="D19" s="78"/>
-      <c r="E19" s="78"/>
-      <c r="F19" s="79"/>
-    </row>
-    <row r="20" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="173"/>
-      <c r="B20" s="120" t="s">
-        <v>226</v>
-      </c>
-      <c r="C20" s="77"/>
-      <c r="D20" s="78"/>
-      <c r="E20" s="78"/>
-      <c r="F20" s="79"/>
-    </row>
-    <row r="21" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="173"/>
-      <c r="B21" s="120" t="s">
+      <c r="C53" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="D53" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="E53" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F53" s="107" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="169"/>
+      <c r="B54" s="70" t="s">
+        <v>250</v>
+      </c>
+      <c r="C54" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="D54" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="E54" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F54" s="107" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="174" t="s">
+        <v>52</v>
+      </c>
+      <c r="B55" s="70" t="s">
         <v>154</v>
       </c>
-      <c r="C21" s="77"/>
-      <c r="D21" s="78"/>
-      <c r="E21" s="78"/>
-      <c r="F21" s="79"/>
-    </row>
-    <row r="22" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="173"/>
-      <c r="B22" s="120" t="s">
+      <c r="C55" s="108" t="s">
+        <v>234</v>
+      </c>
+      <c r="D55" s="108" t="s">
+        <v>234</v>
+      </c>
+      <c r="E55" s="108" t="s">
+        <v>234</v>
+      </c>
+      <c r="F55" s="46" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="175"/>
+      <c r="B56" s="70" t="s">
         <v>155</v>
       </c>
-      <c r="C22" s="77"/>
-      <c r="D22" s="78"/>
-      <c r="E22" s="78"/>
-      <c r="F22" s="79"/>
-    </row>
-    <row r="23" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="173"/>
-      <c r="B23" s="120" t="s">
+      <c r="C56" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="D56" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="E56" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F56" s="46" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="176"/>
+      <c r="B57" s="70" t="s">
         <v>156</v>
       </c>
-      <c r="C23" s="77"/>
-      <c r="D23" s="78"/>
-      <c r="E23" s="78"/>
-      <c r="F23" s="79"/>
-    </row>
-    <row r="24" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="173"/>
-      <c r="B24" s="120" t="s">
+      <c r="C57" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="D57" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="E57" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F57" s="46" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="170" t="s">
+        <v>55</v>
+      </c>
+      <c r="B58" s="70" t="s">
         <v>157</v>
       </c>
-      <c r="C24" s="77"/>
-      <c r="D24" s="78"/>
-      <c r="E24" s="78"/>
-      <c r="F24" s="79"/>
-    </row>
-    <row r="25" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="173"/>
-      <c r="B25" s="120" t="s">
+      <c r="C58" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="D58" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="E58" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F58" s="46" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="170"/>
+      <c r="B59" s="70" t="s">
         <v>158</v>
       </c>
-      <c r="C25" s="77"/>
-      <c r="D25" s="78"/>
-      <c r="E25" s="78"/>
-      <c r="F25" s="79"/>
-    </row>
-    <row r="26" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="173"/>
-      <c r="B26" s="120" t="s">
+      <c r="C59" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="D59" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="E59" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F59" s="46" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="129" t="s">
+        <v>62</v>
+      </c>
+      <c r="B60" s="45" t="s">
         <v>159</v>
       </c>
-      <c r="C26" s="77"/>
-      <c r="D26" s="78"/>
-      <c r="E26" s="78"/>
-      <c r="F26" s="79"/>
-    </row>
-    <row r="27" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="173"/>
-      <c r="B27" s="120" t="s">
+      <c r="C60" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="D60" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="E60" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F60" s="46" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="129"/>
+      <c r="B61" s="45" t="s">
         <v>160</v>
       </c>
-      <c r="C27" s="77"/>
-      <c r="D27" s="78"/>
-      <c r="E27" s="78"/>
-      <c r="F27" s="79"/>
-    </row>
-    <row r="28" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="173"/>
-      <c r="B28" s="120" t="s">
-        <v>229</v>
-      </c>
-      <c r="C28" s="77"/>
-      <c r="D28" s="78"/>
-      <c r="E28" s="78"/>
-      <c r="F28" s="79"/>
-    </row>
-    <row r="29" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="173"/>
-      <c r="B29" s="120" t="s">
-        <v>161</v>
-      </c>
-      <c r="C29" s="77"/>
-      <c r="D29" s="78"/>
-      <c r="E29" s="78"/>
-      <c r="F29" s="79"/>
-    </row>
-    <row r="30" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="173"/>
-      <c r="B30" s="120" t="s">
-        <v>162</v>
-      </c>
-      <c r="C30" s="80"/>
-      <c r="D30" s="81"/>
-      <c r="E30" s="81"/>
-      <c r="F30" s="82"/>
-    </row>
-    <row r="31" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="173"/>
-      <c r="B31" s="120" t="s">
-        <v>163</v>
-      </c>
-      <c r="C31" s="80"/>
-      <c r="D31" s="81"/>
-      <c r="E31" s="81"/>
-      <c r="F31" s="82"/>
-    </row>
-    <row r="32" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="173"/>
-      <c r="B32" s="120" t="s">
-        <v>164</v>
-      </c>
-      <c r="C32" s="83"/>
-      <c r="D32" s="84"/>
-      <c r="E32" s="84"/>
-      <c r="F32" s="85"/>
-    </row>
-    <row r="33" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="173"/>
-      <c r="B33" s="120" t="s">
-        <v>165</v>
-      </c>
-      <c r="C33" s="83"/>
-      <c r="D33" s="84"/>
-      <c r="E33" s="84"/>
-      <c r="F33" s="85"/>
-    </row>
-    <row r="34" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="173"/>
-      <c r="B34" s="120" t="s">
-        <v>166</v>
-      </c>
-      <c r="C34" s="83"/>
-      <c r="D34" s="84"/>
-      <c r="E34" s="84"/>
-      <c r="F34" s="85"/>
-    </row>
-    <row r="35" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="173"/>
-      <c r="B35" s="120" t="s">
-        <v>167</v>
-      </c>
-      <c r="C35" s="83"/>
-      <c r="D35" s="84"/>
-      <c r="E35" s="84"/>
-      <c r="F35" s="86"/>
-    </row>
-    <row r="36" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="60" t="s">
-        <v>66</v>
-      </c>
-      <c r="B36" s="124" t="s">
-        <v>168</v>
-      </c>
-      <c r="C36" s="83"/>
-      <c r="D36" s="84"/>
-      <c r="E36" s="84"/>
-      <c r="F36" s="86"/>
-    </row>
-    <row r="37" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="184" t="s">
-        <v>68</v>
-      </c>
-      <c r="B37" s="120" t="s">
-        <v>169</v>
-      </c>
-      <c r="C37" s="83"/>
-      <c r="D37" s="84"/>
-      <c r="E37" s="84"/>
-      <c r="F37" s="86"/>
-    </row>
-    <row r="38" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="185"/>
-      <c r="B38" s="120" t="s">
-        <v>170</v>
-      </c>
-      <c r="C38" s="83"/>
-      <c r="D38" s="84"/>
-      <c r="E38" s="84"/>
-      <c r="F38" s="86"/>
-    </row>
-    <row r="39" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="185"/>
-      <c r="B39" s="120" t="s">
-        <v>227</v>
-      </c>
-      <c r="C39" s="83"/>
-      <c r="D39" s="84"/>
-      <c r="E39" s="84"/>
-      <c r="F39" s="86"/>
-    </row>
-    <row r="40" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="185"/>
-      <c r="B40" s="120" t="s">
-        <v>171</v>
-      </c>
-      <c r="C40" s="83"/>
-      <c r="D40" s="84"/>
-      <c r="E40" s="84"/>
-      <c r="F40" s="86"/>
-    </row>
-    <row r="41" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="185"/>
-      <c r="B41" s="120" t="s">
-        <v>158</v>
-      </c>
-      <c r="C41" s="83"/>
-      <c r="D41" s="84"/>
-      <c r="E41" s="84"/>
-      <c r="F41" s="86"/>
-    </row>
-    <row r="42" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="185"/>
-      <c r="B42" s="120" t="s">
-        <v>159</v>
-      </c>
-      <c r="C42" s="83"/>
-      <c r="D42" s="84"/>
-      <c r="E42" s="84"/>
-      <c r="F42" s="86"/>
-    </row>
-    <row r="43" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="185"/>
-      <c r="B43" s="120" t="s">
-        <v>172</v>
-      </c>
-      <c r="C43" s="83"/>
-      <c r="D43" s="84"/>
-      <c r="E43" s="84"/>
-      <c r="F43" s="86"/>
-    </row>
-    <row r="44" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="185"/>
-      <c r="B44" s="120" t="s">
-        <v>173</v>
-      </c>
-      <c r="C44" s="83"/>
-      <c r="D44" s="84"/>
-      <c r="E44" s="84"/>
-      <c r="F44" s="86"/>
-    </row>
-    <row r="45" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="185"/>
-      <c r="B45" s="120" t="s">
-        <v>174</v>
-      </c>
-      <c r="C45" s="83"/>
-      <c r="D45" s="84"/>
-      <c r="E45" s="84"/>
-      <c r="F45" s="86"/>
-    </row>
-    <row r="46" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="185"/>
-      <c r="B46" s="120" t="s">
-        <v>175</v>
-      </c>
-      <c r="C46" s="83"/>
-      <c r="D46" s="84"/>
-      <c r="E46" s="84"/>
-      <c r="F46" s="86"/>
-    </row>
-    <row r="47" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="185"/>
-      <c r="B47" s="120" t="s">
-        <v>176</v>
-      </c>
-      <c r="C47" s="83"/>
-      <c r="D47" s="84"/>
-      <c r="E47" s="84"/>
-      <c r="F47" s="86"/>
-    </row>
-    <row r="48" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="185"/>
-      <c r="B48" s="120" t="s">
-        <v>177</v>
-      </c>
-      <c r="C48" s="83"/>
-      <c r="D48" s="84"/>
-      <c r="E48" s="84"/>
-      <c r="F48" s="86"/>
-    </row>
-    <row r="49" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="185"/>
-      <c r="B49" s="120" t="s">
-        <v>178</v>
-      </c>
-      <c r="C49" s="83"/>
-      <c r="D49" s="84"/>
-      <c r="E49" s="84"/>
-      <c r="F49" s="86"/>
-    </row>
-    <row r="50" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="185"/>
-      <c r="B50" s="120" t="s">
-        <v>179</v>
-      </c>
-      <c r="C50" s="83"/>
-      <c r="D50" s="84"/>
-      <c r="E50" s="84"/>
-      <c r="F50" s="86"/>
-    </row>
-    <row r="51" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="186"/>
-      <c r="B51" s="120" t="s">
-        <v>180</v>
-      </c>
-      <c r="C51" s="83"/>
-      <c r="D51" s="84"/>
-      <c r="E51" s="84"/>
-      <c r="F51" s="86"/>
-    </row>
-    <row r="52" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="174" t="s">
-        <v>78</v>
-      </c>
-      <c r="B52" s="120" t="s">
-        <v>181</v>
-      </c>
-      <c r="C52" s="80"/>
-      <c r="D52" s="81"/>
-      <c r="E52" s="81"/>
-      <c r="F52" s="87"/>
-    </row>
-    <row r="53" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="175"/>
-      <c r="B53" s="120" t="s">
-        <v>182</v>
-      </c>
-      <c r="C53" s="80"/>
-      <c r="D53" s="81"/>
-      <c r="E53" s="81"/>
-      <c r="F53" s="87"/>
-    </row>
-    <row r="54" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="176"/>
-      <c r="B54" s="120" t="s">
-        <v>183</v>
-      </c>
-      <c r="C54" s="80"/>
-      <c r="D54" s="81"/>
-      <c r="E54" s="81"/>
-      <c r="F54" s="87"/>
-    </row>
-    <row r="55" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="181" t="s">
-        <v>71</v>
-      </c>
-      <c r="B55" s="120" t="s">
-        <v>184</v>
-      </c>
-      <c r="C55" s="83"/>
-      <c r="D55" s="84"/>
-      <c r="E55" s="84"/>
-      <c r="F55" s="85"/>
-    </row>
-    <row r="56" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="182"/>
-      <c r="B56" s="120" t="s">
-        <v>185</v>
-      </c>
-      <c r="C56" s="83"/>
-      <c r="D56" s="84"/>
-      <c r="E56" s="84"/>
-      <c r="F56" s="85"/>
-    </row>
-    <row r="57" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="183"/>
-      <c r="B57" s="120" t="s">
-        <v>186</v>
-      </c>
-      <c r="C57" s="83"/>
-      <c r="D57" s="84"/>
-      <c r="E57" s="84"/>
-      <c r="F57" s="85"/>
-    </row>
-    <row r="58" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="177" t="s">
-        <v>74</v>
-      </c>
-      <c r="B58" s="120" t="s">
-        <v>187</v>
-      </c>
-      <c r="C58" s="83"/>
-      <c r="D58" s="84"/>
-      <c r="E58" s="84"/>
-      <c r="F58" s="85"/>
-    </row>
-    <row r="59" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="177"/>
-      <c r="B59" s="120" t="s">
-        <v>188</v>
-      </c>
-      <c r="C59" s="83"/>
-      <c r="D59" s="84"/>
-      <c r="E59" s="84"/>
-      <c r="F59" s="86"/>
-    </row>
-    <row r="60" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="136" t="s">
-        <v>81</v>
-      </c>
-      <c r="B60" s="76" t="s">
-        <v>189</v>
-      </c>
-      <c r="C60" s="83"/>
-      <c r="D60" s="84"/>
-      <c r="E60" s="84"/>
-      <c r="F60" s="86"/>
-    </row>
-    <row r="61" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="136"/>
-      <c r="B61" s="76" t="s">
-        <v>190</v>
-      </c>
-      <c r="C61" s="88"/>
-      <c r="D61" s="89"/>
-      <c r="E61" s="89"/>
-      <c r="F61" s="90"/>
+      <c r="C61" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="D61" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="E61" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="F61" s="46" t="s">
+        <v>266</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -4309,209 +4898,281 @@
     <mergeCell ref="A55:A57"/>
     <mergeCell ref="A37:A51"/>
   </mergeCells>
-  <phoneticPr fontId="21" type="noConversion"/>
+  <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:F32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26" style="1" customWidth="1"/>
-    <col min="2" max="2" width="90.58203125" style="1" customWidth="1"/>
-    <col min="3" max="5" width="12.58203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="90.625" style="1" customWidth="1"/>
+    <col min="3" max="5" width="12.625" style="1" customWidth="1"/>
     <col min="6" max="6" width="64.5" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="68" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="69" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="70" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="70" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="70" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="134" t="s">
-        <v>135</v>
-      </c>
-      <c r="B6" s="168" t="s">
-        <v>136</v>
-      </c>
-      <c r="C6" s="149" t="s">
-        <v>137</v>
-      </c>
-      <c r="D6" s="150"/>
-      <c r="E6" s="150"/>
-      <c r="F6" s="168" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="169"/>
-      <c r="B7" s="187"/>
-      <c r="C7" s="71" t="s">
-        <v>47</v>
-      </c>
-      <c r="D7" s="71" t="s">
-        <v>51</v>
-      </c>
-      <c r="E7" s="71" t="s">
-        <v>54</v>
-      </c>
-      <c r="F7" s="188"/>
-    </row>
-    <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="184" t="s">
-        <v>193</v>
-      </c>
-      <c r="B8" s="120" t="s">
-        <v>194</v>
-      </c>
-      <c r="C8" s="91" t="s">
+    <row r="1" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="40" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="41" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="42" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="42" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="42" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="127" t="s">
         <v>106</v>
       </c>
-      <c r="D8" s="92" t="s">
-        <v>140</v>
-      </c>
-      <c r="E8" s="92" t="s">
-        <v>141</v>
-      </c>
-      <c r="F8" s="93" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="185"/>
-      <c r="B9" s="120" t="s">
-        <v>225</v>
-      </c>
-      <c r="C9" s="94"/>
-      <c r="D9" s="78"/>
-      <c r="E9" s="78"/>
-      <c r="F9" s="95"/>
-    </row>
-    <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="185"/>
-      <c r="B10" s="120" t="s">
+      <c r="B6" s="161" t="s">
+        <v>107</v>
+      </c>
+      <c r="C6" s="142" t="s">
+        <v>108</v>
+      </c>
+      <c r="D6" s="143"/>
+      <c r="E6" s="143"/>
+      <c r="F6" s="161" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="162"/>
+      <c r="B7" s="180"/>
+      <c r="C7" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="181"/>
+    </row>
+    <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="177" t="s">
+        <v>163</v>
+      </c>
+      <c r="B8" s="70" t="s">
+        <v>164</v>
+      </c>
+      <c r="C8" s="111" t="s">
+        <v>233</v>
+      </c>
+      <c r="D8" s="112" t="s">
+        <v>233</v>
+      </c>
+      <c r="E8" s="112" t="s">
+        <v>247</v>
+      </c>
+      <c r="F8" s="113" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="178"/>
+      <c r="B9" s="70" t="s">
         <v>195</v>
       </c>
-      <c r="C10" s="94"/>
-      <c r="D10" s="78"/>
-      <c r="E10" s="78"/>
-      <c r="F10" s="95"/>
-    </row>
-    <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="185"/>
-      <c r="B11" s="96" t="s">
-        <v>196</v>
-      </c>
-      <c r="C11" s="97"/>
-      <c r="D11" s="84"/>
-      <c r="E11" s="84"/>
-      <c r="F11" s="98"/>
-    </row>
-    <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="185"/>
-      <c r="B12" s="72" t="s">
-        <v>197</v>
-      </c>
-      <c r="C12" s="97"/>
-      <c r="D12" s="84"/>
-      <c r="E12" s="84"/>
-      <c r="F12" s="98"/>
-    </row>
-    <row r="13" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="185"/>
-      <c r="B13" s="96" t="s">
-        <v>198</v>
-      </c>
-      <c r="C13" s="97"/>
-      <c r="D13" s="84"/>
-      <c r="E13" s="84"/>
-      <c r="F13" s="98"/>
-    </row>
-    <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="185"/>
-      <c r="B14" s="76" t="s">
-        <v>199</v>
-      </c>
-      <c r="C14" s="97"/>
-      <c r="D14" s="84"/>
-      <c r="E14" s="84"/>
-      <c r="F14" s="98"/>
-    </row>
-    <row r="15" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="185"/>
-      <c r="B15" s="96" t="s">
-        <v>200</v>
-      </c>
-      <c r="C15" s="97"/>
-      <c r="D15" s="84"/>
-      <c r="E15" s="84"/>
-      <c r="F15" s="98"/>
-    </row>
-    <row r="16" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="186"/>
-      <c r="B16" s="96" t="s">
-        <v>201</v>
-      </c>
-      <c r="C16" s="97"/>
-      <c r="D16" s="84"/>
-      <c r="E16" s="84"/>
-      <c r="F16" s="98"/>
-    </row>
-    <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="60" t="s">
-        <v>202</v>
-      </c>
-      <c r="B17" s="99" t="s">
-        <v>203</v>
-      </c>
-      <c r="C17" s="100"/>
-      <c r="D17" s="101"/>
-      <c r="E17" s="101"/>
-      <c r="F17" s="102"/>
-    </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="C9" s="114" t="s">
+        <v>235</v>
+      </c>
+      <c r="D9" s="114" t="s">
+        <v>235</v>
+      </c>
+      <c r="E9" s="114" t="s">
+        <v>235</v>
+      </c>
+      <c r="F9" s="115" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="178"/>
+      <c r="B10" s="70" t="s">
+        <v>165</v>
+      </c>
+      <c r="C10" s="114" t="s">
+        <v>235</v>
+      </c>
+      <c r="D10" s="114" t="s">
+        <v>235</v>
+      </c>
+      <c r="E10" s="114" t="s">
+        <v>235</v>
+      </c>
+      <c r="F10" s="115" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="178"/>
+      <c r="B11" s="49" t="s">
+        <v>166</v>
+      </c>
+      <c r="C11" s="116" t="s">
+        <v>267</v>
+      </c>
+      <c r="D11" s="116" t="s">
+        <v>267</v>
+      </c>
+      <c r="E11" s="114" t="s">
+        <v>234</v>
+      </c>
+      <c r="F11" s="60" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="178"/>
+      <c r="B12" s="44" t="s">
+        <v>167</v>
+      </c>
+      <c r="C12" s="116" t="s">
+        <v>268</v>
+      </c>
+      <c r="D12" s="116" t="s">
+        <v>268</v>
+      </c>
+      <c r="E12" s="114" t="s">
+        <v>234</v>
+      </c>
+      <c r="F12" s="60" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="178"/>
+      <c r="B13" s="49" t="s">
+        <v>168</v>
+      </c>
+      <c r="C13" s="116" t="s">
+        <v>269</v>
+      </c>
+      <c r="D13" s="116" t="s">
+        <v>269</v>
+      </c>
+      <c r="E13" s="114" t="s">
+        <v>234</v>
+      </c>
+      <c r="F13" s="60" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="178"/>
+      <c r="B14" s="45" t="s">
+        <v>169</v>
+      </c>
+      <c r="C14" s="116" t="s">
+        <v>234</v>
+      </c>
+      <c r="D14" s="116" t="s">
+        <v>234</v>
+      </c>
+      <c r="E14" s="114" t="s">
+        <v>234</v>
+      </c>
+      <c r="F14" s="60" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="178"/>
+      <c r="B15" s="49" t="s">
+        <v>170</v>
+      </c>
+      <c r="C15" s="116" t="s">
+        <v>234</v>
+      </c>
+      <c r="D15" s="116" t="s">
+        <v>234</v>
+      </c>
+      <c r="E15" s="114" t="s">
+        <v>234</v>
+      </c>
+      <c r="F15" s="60" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="179"/>
+      <c r="B16" s="49" t="s">
+        <v>171</v>
+      </c>
+      <c r="C16" s="116" t="s">
+        <v>234</v>
+      </c>
+      <c r="D16" s="116" t="s">
+        <v>234</v>
+      </c>
+      <c r="E16" s="114" t="s">
+        <v>234</v>
+      </c>
+      <c r="F16" s="60" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="B17" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="C17" s="117" t="s">
+        <v>270</v>
+      </c>
+      <c r="D17" s="117" t="s">
+        <v>270</v>
+      </c>
+      <c r="E17" s="114" t="s">
+        <v>234</v>
+      </c>
+      <c r="F17" s="52" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.2"/>
+    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A6:A7"/>
@@ -4520,240 +5181,240 @@
     <mergeCell ref="F6:F7"/>
     <mergeCell ref="A8:A16"/>
   </mergeCells>
-  <phoneticPr fontId="21" type="noConversion"/>
+  <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:F34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25.75" style="1" customWidth="1"/>
-    <col min="2" max="2" width="92.83203125" style="1" customWidth="1"/>
-    <col min="3" max="5" width="12.58203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="92.875" style="1" customWidth="1"/>
+    <col min="3" max="5" width="12.625" style="1" customWidth="1"/>
     <col min="6" max="6" width="64.5" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="68" t="s">
-        <v>204</v>
-      </c>
-      <c r="B1" s="69"/>
-    </row>
-    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="69" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="70" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="70" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="70" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="103" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="134" t="s">
-        <v>135</v>
-      </c>
-      <c r="B7" s="168" t="s">
-        <v>206</v>
-      </c>
-      <c r="C7" s="149" t="s">
-        <v>137</v>
-      </c>
-      <c r="D7" s="150"/>
-      <c r="E7" s="150"/>
-      <c r="F7" s="168" t="s">
+    <row r="1" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="40" t="s">
+        <v>174</v>
+      </c>
+      <c r="B1" s="41"/>
+    </row>
+    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="41" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="42" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="42" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="42" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="53" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="127" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" s="161" t="s">
+        <v>176</v>
+      </c>
+      <c r="C7" s="142" t="s">
+        <v>108</v>
+      </c>
+      <c r="D7" s="143"/>
+      <c r="E7" s="143"/>
+      <c r="F7" s="161" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="162"/>
+      <c r="B8" s="180"/>
+      <c r="C8" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="181"/>
+    </row>
+    <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="129" t="s">
+        <v>177</v>
+      </c>
+      <c r="B9" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="C9" s="47" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" s="48" t="s">
+        <v>111</v>
+      </c>
+      <c r="E9" s="48" t="s">
+        <v>112</v>
+      </c>
+      <c r="F9" s="54" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="129"/>
+      <c r="B10" s="45" t="s">
+        <v>179</v>
+      </c>
+      <c r="C10" s="55"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="56"/>
+      <c r="F10" s="57"/>
+    </row>
+    <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="129"/>
+      <c r="B11" s="45" t="s">
+        <v>180</v>
+      </c>
+      <c r="C11" s="55"/>
+      <c r="D11" s="56"/>
+      <c r="E11" s="56"/>
+      <c r="F11" s="50"/>
+    </row>
+    <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="129"/>
+      <c r="B12" s="45" t="s">
+        <v>181</v>
+      </c>
+      <c r="C12" s="55"/>
+      <c r="D12" s="56"/>
+      <c r="E12" s="56"/>
+      <c r="F12" s="50"/>
+    </row>
+    <row r="13" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="177" t="s">
+        <v>182</v>
+      </c>
+      <c r="B13" s="45" t="s">
+        <v>183</v>
+      </c>
+      <c r="C13" s="55"/>
+      <c r="D13" s="56"/>
+      <c r="E13" s="56"/>
+      <c r="F13" s="50"/>
+    </row>
+    <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="179"/>
+      <c r="B14" s="58" t="s">
+        <v>184</v>
+      </c>
+      <c r="C14" s="59"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="60"/>
+    </row>
+    <row r="15" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="177" t="s">
+        <v>185</v>
+      </c>
+      <c r="B15" s="45" t="s">
+        <v>186</v>
+      </c>
+      <c r="C15" s="55"/>
+      <c r="D15" s="56"/>
+      <c r="E15" s="56"/>
+      <c r="F15" s="50"/>
+    </row>
+    <row r="16" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="178"/>
+      <c r="B16" s="45" t="s">
+        <v>187</v>
+      </c>
+      <c r="C16" s="55"/>
+      <c r="D16" s="56"/>
+      <c r="E16" s="56"/>
+      <c r="F16" s="50"/>
+    </row>
+    <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="179"/>
+      <c r="B17" s="45" t="s">
+        <v>188</v>
+      </c>
+      <c r="C17" s="61"/>
+      <c r="D17" s="62"/>
+      <c r="E17" s="62"/>
+      <c r="F17" s="63"/>
+    </row>
+    <row r="18" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="34" t="s">
+        <v>189</v>
+      </c>
+      <c r="B18" s="45" t="s">
+        <v>190</v>
+      </c>
+      <c r="C18" s="61"/>
+      <c r="D18" s="62"/>
+      <c r="E18" s="62"/>
+      <c r="F18" s="63"/>
+    </row>
+    <row r="19" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="167" t="s">
+        <v>191</v>
+      </c>
+      <c r="B19" s="45" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="169"/>
-      <c r="B8" s="187"/>
-      <c r="C8" s="71" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="71" t="s">
-        <v>51</v>
-      </c>
-      <c r="E8" s="71" t="s">
-        <v>54</v>
-      </c>
-      <c r="F8" s="188"/>
-    </row>
-    <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="136" t="s">
-        <v>207</v>
-      </c>
-      <c r="B9" s="72" t="s">
-        <v>208</v>
-      </c>
-      <c r="C9" s="91" t="s">
-        <v>106</v>
-      </c>
-      <c r="D9" s="92" t="s">
-        <v>140</v>
-      </c>
-      <c r="E9" s="92" t="s">
-        <v>141</v>
-      </c>
-      <c r="F9" s="104" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="136"/>
-      <c r="B10" s="76" t="s">
-        <v>209</v>
-      </c>
-      <c r="C10" s="105"/>
-      <c r="D10" s="106"/>
-      <c r="E10" s="106"/>
-      <c r="F10" s="107"/>
-    </row>
-    <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="136"/>
-      <c r="B11" s="76" t="s">
-        <v>210</v>
-      </c>
-      <c r="C11" s="105"/>
-      <c r="D11" s="106"/>
-      <c r="E11" s="106"/>
-      <c r="F11" s="98"/>
-    </row>
-    <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="136"/>
-      <c r="B12" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="C12" s="105"/>
-      <c r="D12" s="106"/>
-      <c r="E12" s="106"/>
-      <c r="F12" s="98"/>
-    </row>
-    <row r="13" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="184" t="s">
-        <v>212</v>
-      </c>
-      <c r="B13" s="76" t="s">
-        <v>213</v>
-      </c>
-      <c r="C13" s="105"/>
-      <c r="D13" s="106"/>
-      <c r="E13" s="106"/>
-      <c r="F13" s="98"/>
-    </row>
-    <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="186"/>
-      <c r="B14" s="108" t="s">
-        <v>214</v>
-      </c>
-      <c r="C14" s="109"/>
-      <c r="D14" s="60"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="110"/>
-    </row>
-    <row r="15" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="184" t="s">
-        <v>215</v>
-      </c>
-      <c r="B15" s="76" t="s">
-        <v>216</v>
-      </c>
-      <c r="C15" s="105"/>
-      <c r="D15" s="106"/>
-      <c r="E15" s="106"/>
-      <c r="F15" s="98"/>
-    </row>
-    <row r="16" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="185"/>
-      <c r="B16" s="76" t="s">
-        <v>217</v>
-      </c>
-      <c r="C16" s="105"/>
-      <c r="D16" s="106"/>
-      <c r="E16" s="106"/>
-      <c r="F16" s="98"/>
-    </row>
-    <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="186"/>
-      <c r="B17" s="76" t="s">
-        <v>218</v>
-      </c>
-      <c r="C17" s="111"/>
-      <c r="D17" s="112"/>
-      <c r="E17" s="112"/>
-      <c r="F17" s="113"/>
-    </row>
-    <row r="18" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="60" t="s">
-        <v>219</v>
-      </c>
-      <c r="B18" s="76" t="s">
-        <v>220</v>
-      </c>
-      <c r="C18" s="111"/>
-      <c r="D18" s="112"/>
-      <c r="E18" s="112"/>
-      <c r="F18" s="113"/>
-    </row>
-    <row r="19" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="174" t="s">
-        <v>221</v>
-      </c>
-      <c r="B19" s="76" t="s">
-        <v>222</v>
-      </c>
-      <c r="C19" s="111"/>
-      <c r="D19" s="112"/>
-      <c r="E19" s="112"/>
-      <c r="F19" s="113"/>
-    </row>
-    <row r="20" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="176"/>
-      <c r="B20" s="76" t="s">
-        <v>223</v>
-      </c>
-      <c r="C20" s="114"/>
-      <c r="D20" s="115"/>
-      <c r="E20" s="115"/>
-      <c r="F20" s="116"/>
-    </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="C19" s="61"/>
+      <c r="D19" s="62"/>
+      <c r="E19" s="62"/>
+      <c r="F19" s="63"/>
+    </row>
+    <row r="20" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="169"/>
+      <c r="B20" s="45" t="s">
+        <v>193</v>
+      </c>
+      <c r="C20" s="64"/>
+      <c r="D20" s="65"/>
+      <c r="E20" s="65"/>
+      <c r="F20" s="66"/>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A19:A20"/>
@@ -4765,7 +5426,7 @@
     <mergeCell ref="C7:E7"/>
     <mergeCell ref="A13:A14"/>
   </mergeCells>
-  <phoneticPr fontId="21" type="noConversion"/>
+  <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>

--- a/docs/Npay_단건결제_연동 체크리스트.xlsx
+++ b/docs/Npay_단건결제_연동 체크리스트.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="44265" yWindow="1695" windowWidth="28800" windowHeight="15375" activeTab="2"/>
+    <workbookView xWindow="44265" yWindow="1695" windowWidth="28800" windowHeight="15375" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="검수정보" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="287">
   <si>
     <t>담당자</t>
   </si>
@@ -392,9 +392,6 @@
 SSL은 더 이상 지원하지 않으므로 TLS 1.2 지원 클라이언트 라이브러리 사용</t>
   </si>
   <si>
-    <t>ex. 정상</t>
-  </si>
-  <si>
     <t>방화벽</t>
   </si>
   <si>
@@ -543,15 +540,6 @@
     <t>API 서버 도메인 및 Client ID, Client Secret, ChainId 정상 여부 확인</t>
   </si>
   <si>
-    <t>ex. 비정상</t>
-  </si>
-  <si>
-    <t>ex. 해당 사항 없음</t>
-  </si>
-  <si>
-    <t>ex. 사유 : Mobile App 환경 지원되지 않음</t>
-  </si>
-  <si>
     <t>Npay 환경별로 발급된 가맹점 인증정보를 구분하여 연동 체크</t>
   </si>
   <si>
@@ -862,362 +850,414 @@
   </si>
   <si>
     <t>결제창 호출</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>팝업 사이즈 확인 (툴바 포함 가로: 569px / 세로: 최소 920px)</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>returnUrl 값에 가맹점 개인정보 데이터가 제외되었는지 확인
 (결제정보 외에 개인정보를 제 3자에게 제공시 정보통신망 법률상 약관동의가 필요)</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>cancelReason 개인정보 데이터를 제외 후 전달하는지 확인
 취소사유는 서비스 오픈 후 고객 문의 대응 시 활용하며, 256바이트 미만 전달 필요</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Npay API 요청 파라미터에 이름, 생년월일, 연락처 등 개인정보 데이터가 제외되었는지 확인
 (특히 cancelReason, merchantExtraParameter 등 자유 입력 필드에 개인정보를 기재하는 경우 개인정보보호법 위반에 해당 됨)</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>merchantUserKey 개인정보 데이터가 제외되었는지 확인
 (가맹점에서 구분할 수 있는 사용자 고유의 값으로 연동해야 함)</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>가맹점 인증정보</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>개인정보 보호</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>서원준(hnk1203@naver.com)</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>서원준(hnk1203@naver.com)</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>델리오 (np_gxllc799187)</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>개발환경(  ) / 운영환경( O )</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">naverpay.review@delio.co.kr / Delionpay!2026
 naverpay1.review@delio.co.kr / Delionpay!2026
 </t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">https://www.delio.co.kr — 위 테스트 계정으로 로그인 후 아무 상품이나 장바구니에 담아 결제하면 네이버페이 결제 테스트 가능
 </t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>사용자 전체취소 가능 / 관리자 전체·부분취소 가능</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>평일 09:00 ~ 18:00</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>면세 (신선 과일=농산물 부가세 면세)</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>결제일 + 차주 목요일</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>결제일 + 15일 자동적립</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Npay 발급 대행</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>o</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>x</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>https://www.delio.co.kr</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>https://www.delio.co.kr (반응형)</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>크롬, 사파리, 엣지</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>안드로이드 10 이상 / iOS 15 이상</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>O</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>O</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>O</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>X</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>X</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>주문서(결제) 페이지 네이버페이 결제 시</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>결제 완료 후 서버 검증(웹훅) 시 — 포트원 경유</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>주문생성 실패(재고 부족 등) 시 자동취소 / 고객 주문취소 / 관리자 취소·환불 시 — 모두 포트원 경유</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>PC - page(  ) / popup( O )</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>필수</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>결제 상품에 대한 상품 상세 정보(productItems) 전달은 필수 항목입니다.
 categoryType, categoryId, uid, name, count 는 공통 필수 전달 항목이며,
 그 외 parameter는 결제 상품 유형에 따라 필수 or 선택 항목입니다.
 자세한 내용은 [Npay 개발자센터]를 통해 확인 바랍니다.</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>O 
 (포트원 products 파라미터로 전달)</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>정상</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>정상</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>해당 사항 없음</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>해당 사항 없음</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>해당 사항 없음</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>정상</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Npay 사용을 위해 *.naver.com 도메인 페이지 이동 허용 필요
 -모바일 웹 없음</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>네이버 로그인을 위해 네이버에서 발급하는 쿠키가 만료되지 않도록 설정 필요
 -모바일 웹 없음</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>[네이버 앱 로그인] 사용을 위해 가맹점 앱 Webview scheme 허용 필요
 -모바일 웹 없음</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Npay · 가맹점 주문 체크를 진행하여 주문 누락이 발생되지 않도록 확인 필요
 결제 전 주문데이터 서버 저장(prepare)+웹훅 확정으로 주문 누락 방지 (카드·카카오로 검증됨)</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>※ 결제 승인 / 결제 취소 API: 60초
 ※ 결제 내역 조회 / 현금영수증 금액 조회 / 거래 완료 / 포인트 적립 요청 API: 10초 
 포트원 경유 연동 완료 · 실결제 검증은 검수 오픈 후 진행 예정</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>결제취소 API 요청에 대한 정상 처리 여부 확인 필요
 응답 코드 중 CancelNotComplete는 Npay 취소 진행 중 상태로 
 빠른 시일 내에 자동 취소될 예정이므로 가맹점에서는 취소 성공으로 처리 필요
 -포트원 경유 연동 완료 · 실결제(취소) 검증은 검수 오픈 후 진행 예정</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Npay API 버전 변경 정책 및 변경 기준을 이해하고, 
 사용 및 운영에 문제가 없도록 처리 필요
 -네이버 API 버전은 포트원 채널이 관리 · 검수 시 최종 확인</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Npay 환경별로 발급된 가맹점 인증정보를 구분하여 연동 필요
 -운영환경 인증정보(Client ID·Secret·Chain ID) 포트원 채널 등록 완료</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Npay API 요청 파라미터에 개인정보가 제외되었는지 확인 필요
 -취소사유 등 자유입력 필드에 개인정보 미기재. 결제자 정보는 PG(포트원)에 표준 전달</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>해당 사항 없음</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>정상</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>정상</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>collectChainGroup는 필요시 그룹형 마스터 계정만 연동 되어있는지 확인
 (해당 계정을 마스터로 두는 모든 하위 계정의 결제내역을 조회할 수 있음)</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>PC 팝업, 모바일 페이지 방식(iframe  미사용)</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>포트원이 네이버 규격 팝업 생성 (검수시 확인필요),네이버 이용정지(검수 전)로 결제창을 띄울 수 없어 확인 불가. 검수 오픈 후 확인 예정</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>네이버 이용정지(검수 전)로 결제창을 띄울 수 없어 확인 불가. 검수 오픈 후 확인 예정</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>포트원 경유 연동 · 네이버 이용정지로 실결제 미검증(검수 오픈 후 확인) / 모바일앱 미지원</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>자유입력 필드에 개인정보 미포함(코드 확인) · 포트원 경유 / 모바일앱 미지원</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>포트원 경유 연동 · 네이버 이용정지로 실결제 미검증(검수 오픈 후 확인) / 모바일앱 미지원</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>포트원 경유 연동 · 네이버 이용정지로 실결제 미검증(검수 오픈 후 확인) / 모바일앱 미지원</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>returnUrl에 개인정보 미포함 · 포트원 경유 / 모바일앱 미지원</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>포트원 경유 · 델리오 면세(과일) 처리 검수 시 확인 / 모바일앱 미지원</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>사용자키(merchantUserKey)에 개인정보 미포함(포트원 생성) / 모바일앱 미지원</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>취소사유에 개인정보 미포함(코드 확인) · 포트원 경유 / 모바일앱 미지원</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>포트원 경유 · 델리오 면세(과일) 처리 검수 시 확인 / 모바일앱 미지원</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>포트원 경유 연동 · 네이버 이용정지로 실결제 미검증(검수 오픈 후 확인) / 모바일앱 미지원</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>CancelNotComplete는 취소성공 처리(포트원) · 이용정지로 실검증은 검수 시 / 모바일앱 미지원</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>포트원 대시보드로 조회, 해당 API 직접 미연동</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>델리오 미사용(포트원 경유, 결제일 정산·자동적립)</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>정상</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>정상</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>해당 사항 없음</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>정상</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>실패·취소 시 PG 메시지(resultMessage) alert 표시 — 코드 확인됨 / 모바일앱 미지원</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>승인 실패 시 사유 메시지 alert 표시 — 코드 확인됨 / 모바일앱 미지원</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>네이버 결제화면 영역 · 이용정지로 확인 불가, 검수 오픈 후 확인</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>모바일 앱 없음(웹 전용)</t>
   </si>
   <si>
     <t>표기 '네이버페이'(올바른 공식 표기), 잘못된 표기 없음 / 모바일앱 미지원</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>해당 사항 없음</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>서버측 금액검증(prepare) 적용 · 포트원 경유 / 모바일앱 미지원</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>prepare에서 총결제금액 서버 재계산·검증 — 코드 확인됨 / 모바일앱 미지원</t>
+  </si>
+  <si>
+    <t>수량 변경도 서버에서 금액 재계산·검증(prepare) — 코드 확인됨 / 모바일앱 미지원</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>금액 관련 파라미터는 서버 재계산으로 변조 차단(prepare) — 코드 확인됨 / 모바일앱 미지원</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>결제완료 시 포트원 재조회로 실결제액 검증(webhook/verify) — 코드 확인됨 / 모바일앱 미지원</t>
+  </si>
+  <si>
+    <t>하부가맹점(subMerchantInfo) 미사용</t>
+  </si>
+  <si>
+    <t>취소 금액 서버 검증 · 포트원 경유 / 실결제 취소검증은 검수 시 · 모바일앱 미지원</t>
+  </si>
+  <si>
+    <t>중복 취소 방지(재진입 차단·이미완료 체크) 로직 — 코드 확인됨 / 모바일앱 미지원</t>
+  </si>
+  <si>
+    <t>취소 API 관리자 인증 + 본인 주문 확인으로 타인 취소 차단 — 코드 확인됨 / 모바일앱 미지원</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>RLS + 본인 확인으로 타인 결제정보 접근 차단 — 코드 확인됨 / 모바일앱 미지원</t>
+  </si>
+  <si>
+    <t>리다이렉트 URL은 자사 도메인 고정(외부 URL 불가) — 코드 확인됨 / 모바일앱 미지원</t>
+  </si>
+  <si>
+    <t>연동 로직 변경 시 재검수 요청 인지</t>
+  </si>
+  <si>
+    <t>해당 사항 없음</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>해당 사항 없음</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1328,23 +1368,9 @@
       <charset val="129"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF92D050"/>
-      <name val="나눔고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
       <b/>
       <sz val="15"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="나눔고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="0" tint="-0.34998626667073579"/>
       <name val="나눔고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -1432,7 +1458,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="55">
+  <borders count="53">
     <border>
       <left/>
       <right/>
@@ -2080,8 +2106,8 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
+      <right style="thick">
+        <color theme="3" tint="0.39994506668294322"/>
       </right>
       <top style="thin">
         <color auto="1"/>
@@ -2098,40 +2124,12 @@
       <right style="thick">
         <color theme="3" tint="0.39994506668294322"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thick">
-        <color theme="3" tint="0.39994506668294322"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thick">
-        <color theme="3" tint="0.39994506668294322"/>
-      </right>
       <top style="thick">
         <color theme="3" tint="0.39994506668294322"/>
       </top>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color theme="3" tint="0.39994506668294322"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -2199,11 +2197,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="182">
+  <cellXfs count="172">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2324,7 +2322,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2345,222 +2343,288 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="21" xfId="3" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="21" xfId="3" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2579,13 +2643,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2593,96 +2651,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3051,16 +3019,16 @@
       <c r="A7" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="75" t="s">
-        <v>202</v>
+      <c r="B7" s="62" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="76" t="s">
-        <v>203</v>
+      <c r="B8" s="63" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -3080,130 +3048,130 @@
       <c r="B12" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="155" t="s">
+      <c r="C12" s="108" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="155"/>
+      <c r="D12" s="108"/>
     </row>
     <row r="13" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="77" t="s">
-        <v>204</v>
-      </c>
-      <c r="C13" s="151" t="s">
+      <c r="B13" s="64" t="s">
+        <v>200</v>
+      </c>
+      <c r="C13" s="109" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="152"/>
+      <c r="D13" s="110"/>
     </row>
     <row r="14" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="78" t="s">
-        <v>205</v>
-      </c>
-      <c r="C14" s="156" t="s">
+      <c r="B14" s="65" t="s">
+        <v>201</v>
+      </c>
+      <c r="C14" s="111" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="157"/>
+      <c r="D14" s="112"/>
     </row>
     <row r="15" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="79" t="s">
-        <v>206</v>
-      </c>
-      <c r="C15" s="158" t="s">
+      <c r="B15" s="66" t="s">
+        <v>202</v>
+      </c>
+      <c r="C15" s="113" t="s">
         <v>17</v>
       </c>
-      <c r="D15" s="159"/>
+      <c r="D15" s="114"/>
     </row>
     <row r="16" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A16" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="79" t="s">
-        <v>207</v>
-      </c>
-      <c r="C16" s="151" t="s">
+      <c r="B16" s="66" t="s">
+        <v>203</v>
+      </c>
+      <c r="C16" s="109" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="152"/>
+      <c r="D16" s="110"/>
     </row>
     <row r="17" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="80" t="s">
-        <v>208</v>
-      </c>
-      <c r="C17" s="151" t="s">
+      <c r="B17" s="67" t="s">
+        <v>204</v>
+      </c>
+      <c r="C17" s="109" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="152"/>
+      <c r="D17" s="110"/>
     </row>
     <row r="18" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="81" t="s">
-        <v>209</v>
-      </c>
-      <c r="C18" s="153" t="s">
+      <c r="B18" s="68" t="s">
+        <v>205</v>
+      </c>
+      <c r="C18" s="115" t="s">
         <v>23</v>
       </c>
-      <c r="D18" s="154"/>
+      <c r="D18" s="116"/>
     </row>
     <row r="19" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="82" t="s">
-        <v>210</v>
-      </c>
-      <c r="C19" s="140" t="s">
+      <c r="B19" s="69" t="s">
+        <v>206</v>
+      </c>
+      <c r="C19" s="117" t="s">
         <v>25</v>
       </c>
-      <c r="D19" s="141"/>
+      <c r="D19" s="118"/>
     </row>
     <row r="20" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="83" t="s">
-        <v>211</v>
-      </c>
-      <c r="C20" s="140" t="s">
+      <c r="B20" s="70" t="s">
+        <v>207</v>
+      </c>
+      <c r="C20" s="117" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="141"/>
+      <c r="D20" s="118"/>
     </row>
     <row r="21" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="84" t="s">
-        <v>212</v>
-      </c>
-      <c r="C21" s="140" t="s">
+      <c r="B21" s="71" t="s">
+        <v>208</v>
+      </c>
+      <c r="C21" s="117" t="s">
         <v>29</v>
       </c>
-      <c r="D21" s="141"/>
+      <c r="D21" s="118"/>
     </row>
     <row r="22" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="85" t="s">
-        <v>213</v>
-      </c>
-      <c r="C22" s="140" t="s">
+      <c r="B22" s="72" t="s">
+        <v>209</v>
+      </c>
+      <c r="C22" s="117" t="s">
         <v>31</v>
       </c>
-      <c r="D22" s="141"/>
+      <c r="D22" s="118"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="11"/>
@@ -3213,7 +3181,7 @@
       <c r="A25" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B25" s="74" t="s">
+      <c r="B25" s="61" t="s">
         <v>33</v>
       </c>
       <c r="C25" s="9" t="s">
@@ -3228,14 +3196,14 @@
       <c r="A26" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B26" s="86" t="s">
+      <c r="B26" s="73" t="s">
+        <v>210</v>
+      </c>
+      <c r="C26" s="75" t="s">
+        <v>212</v>
+      </c>
+      <c r="D26" s="78" t="s">
         <v>214</v>
-      </c>
-      <c r="C26" s="88" t="s">
-        <v>216</v>
-      </c>
-      <c r="D26" s="91" t="s">
-        <v>218</v>
       </c>
       <c r="E26" s="20"/>
     </row>
@@ -3243,14 +3211,14 @@
       <c r="A27" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="59" t="s">
-        <v>214</v>
-      </c>
-      <c r="C27" s="89" t="s">
-        <v>217</v>
-      </c>
-      <c r="D27" s="92" t="s">
-        <v>219</v>
+      <c r="B27" s="52" t="s">
+        <v>210</v>
+      </c>
+      <c r="C27" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="D27" s="79" t="s">
+        <v>215</v>
       </c>
       <c r="E27" s="20"/>
     </row>
@@ -3258,13 +3226,13 @@
       <c r="A28" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="87" t="s">
-        <v>215</v>
-      </c>
-      <c r="C28" s="90" t="s">
+      <c r="B28" s="74" t="s">
+        <v>211</v>
+      </c>
+      <c r="C28" s="77" t="s">
         <v>40</v>
       </c>
-      <c r="D28" s="93" t="s">
+      <c r="D28" s="80" t="s">
         <v>38</v>
       </c>
       <c r="E28" s="20"/>
@@ -3287,40 +3255,40 @@
       <c r="D32" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="E32" s="142" t="s">
+      <c r="E32" s="119" t="s">
         <v>46</v>
       </c>
-      <c r="F32" s="143"/>
-      <c r="G32" s="143"/>
-      <c r="H32" s="143"/>
-      <c r="I32" s="143"/>
-      <c r="J32" s="143"/>
-      <c r="K32" s="143"/>
-      <c r="L32" s="144"/>
+      <c r="F32" s="120"/>
+      <c r="G32" s="120"/>
+      <c r="H32" s="120"/>
+      <c r="I32" s="120"/>
+      <c r="J32" s="120"/>
+      <c r="K32" s="120"/>
+      <c r="L32" s="121"/>
     </row>
     <row r="33" spans="1:12" ht="20.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A33" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="B33" s="68" t="s">
-        <v>194</v>
-      </c>
-      <c r="C33" s="94" t="s">
-        <v>220</v>
-      </c>
-      <c r="D33" s="96" t="s">
-        <v>225</v>
-      </c>
-      <c r="E33" s="145" t="s">
+      <c r="B33" s="55" t="s">
+        <v>190</v>
+      </c>
+      <c r="C33" s="81" t="s">
+        <v>216</v>
+      </c>
+      <c r="D33" s="83" t="s">
+        <v>221</v>
+      </c>
+      <c r="E33" s="122" t="s">
         <v>48</v>
       </c>
-      <c r="F33" s="146"/>
-      <c r="G33" s="146"/>
-      <c r="H33" s="146"/>
-      <c r="I33" s="146"/>
-      <c r="J33" s="146"/>
-      <c r="K33" s="146"/>
-      <c r="L33" s="141"/>
+      <c r="F33" s="123"/>
+      <c r="G33" s="123"/>
+      <c r="H33" s="123"/>
+      <c r="I33" s="123"/>
+      <c r="J33" s="123"/>
+      <c r="K33" s="123"/>
+      <c r="L33" s="118"/>
     </row>
     <row r="34" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="24" t="s">
@@ -3329,22 +3297,22 @@
       <c r="B34" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="C34" s="59" t="s">
-        <v>221</v>
+      <c r="C34" s="52" t="s">
+        <v>217</v>
       </c>
       <c r="D34" s="46" t="s">
-        <v>226</v>
-      </c>
-      <c r="E34" s="147" t="s">
+        <v>222</v>
+      </c>
+      <c r="E34" s="124" t="s">
         <v>48</v>
       </c>
-      <c r="F34" s="148"/>
-      <c r="G34" s="148"/>
-      <c r="H34" s="148"/>
-      <c r="I34" s="148"/>
-      <c r="J34" s="148"/>
-      <c r="K34" s="148"/>
-      <c r="L34" s="149"/>
+      <c r="F34" s="125"/>
+      <c r="G34" s="125"/>
+      <c r="H34" s="125"/>
+      <c r="I34" s="125"/>
+      <c r="J34" s="125"/>
+      <c r="K34" s="125"/>
+      <c r="L34" s="126"/>
     </row>
     <row r="35" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="24" t="s">
@@ -3353,22 +3321,22 @@
       <c r="B35" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="C35" s="59" t="s">
-        <v>222</v>
-      </c>
-      <c r="D35" s="97" t="s">
-        <v>227</v>
-      </c>
-      <c r="E35" s="150" t="s">
+      <c r="C35" s="52" t="s">
+        <v>218</v>
+      </c>
+      <c r="D35" s="84" t="s">
+        <v>223</v>
+      </c>
+      <c r="E35" s="127" t="s">
         <v>48</v>
       </c>
-      <c r="F35" s="136"/>
-      <c r="G35" s="136"/>
-      <c r="H35" s="136"/>
-      <c r="I35" s="136"/>
-      <c r="J35" s="136"/>
-      <c r="K35" s="136"/>
-      <c r="L35" s="137"/>
+      <c r="F35" s="128"/>
+      <c r="G35" s="128"/>
+      <c r="H35" s="128"/>
+      <c r="I35" s="128"/>
+      <c r="J35" s="128"/>
+      <c r="K35" s="128"/>
+      <c r="L35" s="129"/>
     </row>
     <row r="36" spans="1:12" ht="75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="24" t="s">
@@ -3377,8 +3345,8 @@
       <c r="B36" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="59" t="s">
-        <v>223</v>
+      <c r="C36" s="52" t="s">
+        <v>219</v>
       </c>
       <c r="D36" s="28" t="s">
         <v>53</v>
@@ -3401,8 +3369,8 @@
       <c r="B37" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="C37" s="59" t="s">
-        <v>223</v>
+      <c r="C37" s="52" t="s">
+        <v>219</v>
       </c>
       <c r="D37" s="26" t="s">
         <v>56</v>
@@ -3425,8 +3393,8 @@
       <c r="B38" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="C38" s="59" t="s">
-        <v>224</v>
+      <c r="C38" s="52" t="s">
+        <v>220</v>
       </c>
       <c r="D38" s="26" t="s">
         <v>60</v>
@@ -3434,13 +3402,13 @@
       <c r="E38" s="135" t="s">
         <v>61</v>
       </c>
-      <c r="F38" s="136"/>
-      <c r="G38" s="136"/>
-      <c r="H38" s="136"/>
-      <c r="I38" s="136"/>
-      <c r="J38" s="136"/>
-      <c r="K38" s="136"/>
-      <c r="L38" s="137"/>
+      <c r="F38" s="128"/>
+      <c r="G38" s="128"/>
+      <c r="H38" s="128"/>
+      <c r="I38" s="128"/>
+      <c r="J38" s="128"/>
+      <c r="K38" s="128"/>
+      <c r="L38" s="129"/>
     </row>
     <row r="39" spans="1:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A39" s="30" t="s">
@@ -3449,8 +3417,8 @@
       <c r="B39" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="C39" s="95" t="s">
-        <v>223</v>
+      <c r="C39" s="82" t="s">
+        <v>219</v>
       </c>
       <c r="D39" s="31" t="s">
         <v>56</v>
@@ -3458,17 +3426,17 @@
       <c r="E39" s="135" t="s">
         <v>63</v>
       </c>
-      <c r="F39" s="138"/>
-      <c r="G39" s="138"/>
-      <c r="H39" s="138"/>
-      <c r="I39" s="138"/>
-      <c r="J39" s="138"/>
-      <c r="K39" s="138"/>
-      <c r="L39" s="139"/>
+      <c r="F39" s="136"/>
+      <c r="G39" s="136"/>
+      <c r="H39" s="136"/>
+      <c r="I39" s="136"/>
+      <c r="J39" s="136"/>
+      <c r="K39" s="136"/>
+      <c r="L39" s="137"/>
     </row>
     <row r="40" spans="1:12" ht="13.5" thickTop="1" x14ac:dyDescent="0.2"/>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A42" s="69" t="s">
+      <c r="A42" s="56" t="s">
         <v>64</v>
       </c>
     </row>
@@ -3479,30 +3447,30 @@
       <c r="B43" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C43" s="125" t="s">
+      <c r="C43" s="138" t="s">
         <v>46</v>
       </c>
-      <c r="D43" s="127"/>
+      <c r="D43" s="139"/>
     </row>
     <row r="44" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="119" t="s">
+      <c r="A44" s="141" t="s">
         <v>66</v>
       </c>
-      <c r="B44" s="98" t="s">
-        <v>228</v>
-      </c>
-      <c r="C44" s="121" t="s">
+      <c r="B44" s="85" t="s">
+        <v>224</v>
+      </c>
+      <c r="C44" s="143" t="s">
         <v>67</v>
       </c>
-      <c r="D44" s="122"/>
+      <c r="D44" s="144"/>
     </row>
     <row r="45" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="120"/>
-      <c r="B45" s="99" t="s">
+      <c r="A45" s="142"/>
+      <c r="B45" s="86" t="s">
         <v>68</v>
       </c>
-      <c r="C45" s="123"/>
-      <c r="D45" s="124"/>
+      <c r="C45" s="145"/>
+      <c r="D45" s="146"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" s="11"/>
@@ -3531,38 +3499,38 @@
       <c r="D49" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="E49" s="125" t="s">
+      <c r="E49" s="138" t="s">
         <v>46</v>
       </c>
-      <c r="F49" s="126"/>
-      <c r="G49" s="126"/>
-      <c r="H49" s="126"/>
-      <c r="I49" s="126"/>
-      <c r="J49" s="126"/>
-      <c r="K49" s="126"/>
-      <c r="L49" s="127"/>
+      <c r="F49" s="147"/>
+      <c r="G49" s="147"/>
+      <c r="H49" s="147"/>
+      <c r="I49" s="147"/>
+      <c r="J49" s="147"/>
+      <c r="K49" s="147"/>
+      <c r="L49" s="139"/>
     </row>
     <row r="50" spans="1:12" ht="206.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="24" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B50" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="C50" s="101" t="s">
-        <v>231</v>
-      </c>
-      <c r="D50" s="100"/>
-      <c r="E50" s="128" t="s">
-        <v>230</v>
-      </c>
-      <c r="F50" s="129"/>
-      <c r="G50" s="129"/>
-      <c r="H50" s="129"/>
-      <c r="I50" s="129"/>
-      <c r="J50" s="129"/>
-      <c r="K50" s="129"/>
-      <c r="L50" s="129"/>
+      <c r="C50" s="88" t="s">
+        <v>227</v>
+      </c>
+      <c r="D50" s="87"/>
+      <c r="E50" s="148" t="s">
+        <v>226</v>
+      </c>
+      <c r="F50" s="149"/>
+      <c r="G50" s="149"/>
+      <c r="H50" s="149"/>
+      <c r="I50" s="149"/>
+      <c r="J50" s="149"/>
+      <c r="K50" s="149"/>
+      <c r="L50" s="149"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" s="35"/>
@@ -3628,8 +3596,8 @@
       <c r="D58" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="E58" s="102" t="s">
-        <v>232</v>
+      <c r="E58" s="89" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="59" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -3637,59 +3605,59 @@
         <v>47</v>
       </c>
       <c r="B59" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="C59" s="39" t="s">
         <v>85</v>
       </c>
-      <c r="C59" s="39" t="s">
+      <c r="D59" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="D59" s="19" t="s">
+      <c r="E59" s="89" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="140" t="s">
+        <v>47</v>
+      </c>
+      <c r="B60" s="140" t="s">
         <v>87</v>
       </c>
-      <c r="E59" s="102" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="118" t="s">
-        <v>47</v>
-      </c>
-      <c r="B60" s="118" t="s">
+      <c r="C60" s="39" t="s">
         <v>88</v>
       </c>
-      <c r="C60" s="39" t="s">
+      <c r="D60" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="E60" s="89" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="140"/>
+      <c r="B61" s="140"/>
+      <c r="C61" s="39" t="s">
         <v>89</v>
       </c>
-      <c r="D60" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="E60" s="102" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="118"/>
-      <c r="B61" s="118"/>
-      <c r="C61" s="39" t="s">
+      <c r="D61" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="E61" s="89" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="140"/>
+      <c r="B62" s="140"/>
+      <c r="C62" s="39" t="s">
         <v>90</v>
       </c>
-      <c r="D61" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="E61" s="102" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="118"/>
-      <c r="B62" s="118"/>
-      <c r="C62" s="39" t="s">
-        <v>91</v>
-      </c>
       <c r="D62" s="19" t="s">
-        <v>240</v>
-      </c>
-      <c r="E62" s="102" t="s">
         <v>236</v>
+      </c>
+      <c r="E62" s="89" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="63" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -3697,117 +3665,97 @@
         <v>47</v>
       </c>
       <c r="B63" s="39" t="s">
+        <v>91</v>
+      </c>
+      <c r="C63" s="39" t="s">
         <v>92</v>
       </c>
-      <c r="C63" s="39" t="s">
-        <v>93</v>
-      </c>
       <c r="D63" s="19" t="s">
-        <v>241</v>
-      </c>
-      <c r="E63" s="102" t="s">
-        <v>233</v>
+        <v>237</v>
+      </c>
+      <c r="E63" s="89" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A64" s="39" t="s">
+        <v>93</v>
+      </c>
+      <c r="B64" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="B64" s="39" t="s">
+      <c r="C64" s="39" t="s">
         <v>95</v>
       </c>
-      <c r="C64" s="39" t="s">
-        <v>96</v>
-      </c>
       <c r="D64" s="19" t="s">
-        <v>242</v>
-      </c>
-      <c r="E64" s="102" t="s">
-        <v>232</v>
+        <v>238</v>
+      </c>
+      <c r="E64" s="89" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A65" s="39" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B65" s="39" t="s">
+        <v>96</v>
+      </c>
+      <c r="C65" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="C65" s="39" t="s">
+      <c r="D65" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="E65" s="89" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A66" s="140" t="s">
+        <v>93</v>
+      </c>
+      <c r="B66" s="140" t="s">
         <v>98</v>
       </c>
-      <c r="D65" s="19" t="s">
-        <v>243</v>
-      </c>
-      <c r="E65" s="102" t="s">
+      <c r="C66" s="39" t="s">
+        <v>99</v>
+      </c>
+      <c r="D66" s="19" t="s">
+        <v>240</v>
+      </c>
+      <c r="E66" s="89" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A66" s="118" t="s">
-        <v>94</v>
-      </c>
-      <c r="B66" s="118" t="s">
-        <v>99</v>
-      </c>
-      <c r="C66" s="39" t="s">
-        <v>100</v>
-      </c>
-      <c r="D66" s="19" t="s">
-        <v>244</v>
-      </c>
-      <c r="E66" s="102" t="s">
-        <v>237</v>
-      </c>
-    </row>
     <row r="67" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="118"/>
-      <c r="B67" s="118"/>
-      <c r="C67" s="67" t="s">
-        <v>200</v>
+      <c r="A67" s="140"/>
+      <c r="B67" s="140"/>
+      <c r="C67" s="54" t="s">
+        <v>196</v>
       </c>
       <c r="D67" s="19" t="s">
-        <v>245</v>
-      </c>
-      <c r="E67" s="103" t="s">
-        <v>232</v>
+        <v>241</v>
+      </c>
+      <c r="E67" s="90" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="118"/>
-      <c r="B68" s="118"/>
-      <c r="C68" s="71" t="s">
-        <v>201</v>
-      </c>
-      <c r="D68" s="72" t="s">
-        <v>246</v>
-      </c>
-      <c r="E68" s="104" t="s">
-        <v>232</v>
+      <c r="A68" s="140"/>
+      <c r="B68" s="140"/>
+      <c r="C68" s="58" t="s">
+        <v>197</v>
+      </c>
+      <c r="D68" s="59" t="s">
+        <v>242</v>
+      </c>
+      <c r="E68" s="91" t="s">
+        <v>228</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E32:L32"/>
-    <mergeCell ref="E33:L33"/>
-    <mergeCell ref="E34:L34"/>
-    <mergeCell ref="E35:L35"/>
-    <mergeCell ref="E36:L36"/>
-    <mergeCell ref="E37:L37"/>
-    <mergeCell ref="E38:L38"/>
-    <mergeCell ref="E39:L39"/>
-    <mergeCell ref="C43:D43"/>
     <mergeCell ref="A66:A68"/>
     <mergeCell ref="B66:B68"/>
     <mergeCell ref="A44:A45"/>
@@ -3816,8 +3764,28 @@
     <mergeCell ref="E50:L50"/>
     <mergeCell ref="A60:A62"/>
     <mergeCell ref="B60:B62"/>
+    <mergeCell ref="E36:L36"/>
+    <mergeCell ref="E37:L37"/>
+    <mergeCell ref="E38:L38"/>
+    <mergeCell ref="E39:L39"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E32:L32"/>
+    <mergeCell ref="E33:L33"/>
+    <mergeCell ref="E34:L34"/>
+    <mergeCell ref="E35:L35"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
   </mergeCells>
-  <phoneticPr fontId="20" type="noConversion"/>
+  <phoneticPr fontId="18" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="C26" r:id="rId1"/>
   </hyperlinks>
@@ -3843,48 +3811,48 @@
   <sheetData>
     <row r="1" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="40" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="41" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="42" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="42" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="42" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="139" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="127" t="s">
+      <c r="B6" s="138" t="s">
         <v>106</v>
       </c>
-      <c r="B6" s="125" t="s">
+      <c r="C6" s="154" t="s">
         <v>107</v>
       </c>
-      <c r="C6" s="164" t="s">
+      <c r="D6" s="154"/>
+      <c r="E6" s="154"/>
+      <c r="F6" s="150" t="s">
         <v>108</v>
       </c>
-      <c r="D6" s="164"/>
-      <c r="E6" s="164"/>
-      <c r="F6" s="160" t="s">
-        <v>109</v>
-      </c>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="162"/>
-      <c r="B7" s="163"/>
+      <c r="A7" s="152"/>
+      <c r="B7" s="153"/>
       <c r="C7" s="43" t="s">
         <v>36</v>
       </c>
@@ -3894,994 +3862,994 @@
       <c r="E7" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="F7" s="161"/>
+      <c r="F7" s="151"/>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="171" t="s">
-        <v>99</v>
+      <c r="A8" s="161" t="s">
+        <v>98</v>
       </c>
       <c r="B8" s="44" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8" s="96" t="s">
+        <v>229</v>
+      </c>
+      <c r="D8" s="97" t="s">
+        <v>228</v>
+      </c>
+      <c r="E8" s="97" t="s">
+        <v>243</v>
+      </c>
+      <c r="F8" s="94" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="162"/>
+      <c r="B9" s="45" t="s">
         <v>110</v>
       </c>
-      <c r="C8" s="109" t="s">
-        <v>233</v>
-      </c>
-      <c r="D8" s="110" t="s">
-        <v>232</v>
-      </c>
-      <c r="E8" s="110" t="s">
-        <v>247</v>
-      </c>
-      <c r="F8" s="107" t="s">
+      <c r="C9" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D9" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E9" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F9" s="94" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="162"/>
+      <c r="B10" s="45" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D10" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E10" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F10" s="94" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="162"/>
+      <c r="B11" s="45" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D11" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E11" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F11" s="94" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="162"/>
+      <c r="B12" s="45" t="s">
+        <v>113</v>
+      </c>
+      <c r="C12" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D12" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E12" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F12" s="94" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="162"/>
+      <c r="B13" s="57" t="s">
+        <v>194</v>
+      </c>
+      <c r="C13" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D13" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E13" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F13" s="94" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="162"/>
+      <c r="B14" s="57" t="s">
+        <v>114</v>
+      </c>
+      <c r="C14" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D14" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E14" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F14" s="94" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="163"/>
+      <c r="B15" s="57" t="s">
+        <v>115</v>
+      </c>
+      <c r="C15" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D15" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E15" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F15" s="94" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="155" t="s">
+        <v>116</v>
+      </c>
+      <c r="B16" s="57" t="s">
+        <v>117</v>
+      </c>
+      <c r="C16" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D16" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E16" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F16" s="94" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="156"/>
+      <c r="B17" s="57" t="s">
+        <v>118</v>
+      </c>
+      <c r="C17" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D17" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E17" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F17" s="94" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="156"/>
+      <c r="B18" s="57" t="s">
+        <v>119</v>
+      </c>
+      <c r="C18" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D18" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E18" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F18" s="94" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="156"/>
+      <c r="B19" s="57" t="s">
+        <v>120</v>
+      </c>
+      <c r="C19" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D19" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E19" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F19" s="94" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="156"/>
+      <c r="B20" s="57" t="s">
+        <v>192</v>
+      </c>
+      <c r="C20" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D20" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E20" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F20" s="94" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="156"/>
+      <c r="B21" s="57" t="s">
+        <v>121</v>
+      </c>
+      <c r="C21" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D21" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E21" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F21" s="94" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="156"/>
+      <c r="B22" s="57" t="s">
+        <v>122</v>
+      </c>
+      <c r="C22" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D22" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E22" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F22" s="94" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="156"/>
+      <c r="B23" s="57" t="s">
+        <v>123</v>
+      </c>
+      <c r="C23" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D23" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E23" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F23" s="94" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="156"/>
+      <c r="B24" s="57" t="s">
+        <v>124</v>
+      </c>
+      <c r="C24" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D24" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E24" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F24" s="94" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="156"/>
+      <c r="B25" s="57" t="s">
+        <v>125</v>
+      </c>
+      <c r="C25" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D25" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E25" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F25" s="94" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="156"/>
+      <c r="B26" s="57" t="s">
+        <v>126</v>
+      </c>
+      <c r="C26" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D26" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E26" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F26" s="94" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="156"/>
+      <c r="B27" s="57" t="s">
+        <v>127</v>
+      </c>
+      <c r="C27" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D27" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E27" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F27" s="94" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="156"/>
+      <c r="B28" s="57" t="s">
+        <v>195</v>
+      </c>
+      <c r="C28" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D28" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E28" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F28" s="94" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="172"/>
-      <c r="B9" s="45" t="s">
-        <v>114</v>
-      </c>
-      <c r="C9" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="D9" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="E9" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F9" s="107" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="172"/>
-      <c r="B10" s="45" t="s">
-        <v>115</v>
-      </c>
-      <c r="C10" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="D10" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="E10" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F10" s="107" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="172"/>
-      <c r="B11" s="45" t="s">
-        <v>116</v>
-      </c>
-      <c r="C11" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="D11" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="E11" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F11" s="107" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="172"/>
-      <c r="B12" s="45" t="s">
-        <v>117</v>
-      </c>
-      <c r="C12" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="D12" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="E12" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F12" s="107" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="172"/>
-      <c r="B13" s="70" t="s">
-        <v>198</v>
-      </c>
-      <c r="C13" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="D13" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="E13" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F13" s="107" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="172"/>
-      <c r="B14" s="70" t="s">
-        <v>118</v>
-      </c>
-      <c r="C14" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="D14" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="E14" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F14" s="107" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="173"/>
-      <c r="B15" s="70" t="s">
-        <v>119</v>
-      </c>
-      <c r="C15" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="D15" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="E15" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F15" s="107" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="165" t="s">
-        <v>120</v>
-      </c>
-      <c r="B16" s="70" t="s">
-        <v>121</v>
-      </c>
-      <c r="C16" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="D16" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="E16" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F16" s="107" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="166"/>
-      <c r="B17" s="70" t="s">
-        <v>122</v>
-      </c>
-      <c r="C17" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="D17" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="E17" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F17" s="107" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="166"/>
-      <c r="B18" s="70" t="s">
-        <v>123</v>
-      </c>
-      <c r="C18" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="D18" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="E18" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F18" s="107" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="166"/>
-      <c r="B19" s="70" t="s">
-        <v>124</v>
-      </c>
-      <c r="C19" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="D19" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="E19" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F19" s="107" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="166"/>
-      <c r="B20" s="70" t="s">
-        <v>196</v>
-      </c>
-      <c r="C20" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="D20" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="E20" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F20" s="107" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="166"/>
-      <c r="B21" s="70" t="s">
-        <v>125</v>
-      </c>
-      <c r="C21" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="D21" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="E21" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F21" s="107" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="166"/>
-      <c r="B22" s="70" t="s">
-        <v>126</v>
-      </c>
-      <c r="C22" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="D22" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="E22" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F22" s="107" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="166"/>
-      <c r="B23" s="70" t="s">
-        <v>127</v>
-      </c>
-      <c r="C23" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="D23" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="E23" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F23" s="107" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="166"/>
-      <c r="B24" s="70" t="s">
+    <row r="29" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="156"/>
+      <c r="B29" s="57" t="s">
         <v>128</v>
       </c>
-      <c r="C24" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="D24" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="E24" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F24" s="107" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="166"/>
-      <c r="B25" s="70" t="s">
+      <c r="C29" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D29" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E29" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F29" s="94" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="156"/>
+      <c r="B30" s="57" t="s">
         <v>129</v>
       </c>
-      <c r="C25" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="D25" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="E25" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F25" s="107" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="166"/>
-      <c r="B26" s="70" t="s">
+      <c r="C30" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D30" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E30" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F30" s="94" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="156"/>
+      <c r="B31" s="57" t="s">
         <v>130</v>
       </c>
-      <c r="C26" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="D26" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="E26" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F26" s="107" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="166"/>
-      <c r="B27" s="70" t="s">
+      <c r="C31" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D31" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E31" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F31" s="94" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="156"/>
+      <c r="B32" s="57" t="s">
         <v>131</v>
       </c>
-      <c r="C27" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="D27" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="E27" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F27" s="107" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="166"/>
-      <c r="B28" s="70" t="s">
-        <v>199</v>
-      </c>
-      <c r="C28" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="D28" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="E28" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F28" s="107" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="166"/>
-      <c r="B29" s="70" t="s">
+      <c r="C32" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D32" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E32" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F32" s="94" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="156"/>
+      <c r="B33" s="57" t="s">
         <v>132</v>
       </c>
-      <c r="C29" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="D29" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="E29" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F29" s="107" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="166"/>
-      <c r="B30" s="70" t="s">
+      <c r="C33" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D33" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E33" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F33" s="94" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="156"/>
+      <c r="B34" s="57" t="s">
         <v>133</v>
       </c>
-      <c r="C30" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="D30" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="E30" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F30" s="107" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="166"/>
-      <c r="B31" s="70" t="s">
+      <c r="C34" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D34" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E34" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F34" s="94" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="156"/>
+      <c r="B35" s="57" t="s">
         <v>134</v>
       </c>
-      <c r="C31" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="D31" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="E31" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F31" s="107" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="166"/>
-      <c r="B32" s="70" t="s">
-        <v>135</v>
-      </c>
-      <c r="C32" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="D32" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="E32" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F32" s="107" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="166"/>
-      <c r="B33" s="70" t="s">
-        <v>136</v>
-      </c>
-      <c r="C33" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="D33" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="E33" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F33" s="107" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="166"/>
-      <c r="B34" s="70" t="s">
-        <v>137</v>
-      </c>
-      <c r="C34" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="D34" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="E34" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F34" s="107" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="166"/>
-      <c r="B35" s="70" t="s">
-        <v>138</v>
-      </c>
-      <c r="C35" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="D35" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="E35" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F35" s="107" t="s">
-        <v>256</v>
+      <c r="C35" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D35" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E35" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F35" s="94" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="B36" s="73" t="s">
+      <c r="B36" s="60" t="s">
+        <v>135</v>
+      </c>
+      <c r="C36" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D36" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E36" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F36" s="94" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="167" t="s">
+        <v>50</v>
+      </c>
+      <c r="B37" s="57" t="s">
+        <v>136</v>
+      </c>
+      <c r="C37" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D37" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E37" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F37" s="94" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="168"/>
+      <c r="B38" s="57" t="s">
+        <v>137</v>
+      </c>
+      <c r="C38" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D38" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E38" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F38" s="94" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="168"/>
+      <c r="B39" s="57" t="s">
+        <v>193</v>
+      </c>
+      <c r="C39" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D39" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E39" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F39" s="94" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="168"/>
+      <c r="B40" s="57" t="s">
+        <v>138</v>
+      </c>
+      <c r="C40" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D40" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E40" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F40" s="94" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="168"/>
+      <c r="B41" s="57" t="s">
+        <v>125</v>
+      </c>
+      <c r="C41" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D41" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E41" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F41" s="94" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="168"/>
+      <c r="B42" s="57" t="s">
+        <v>126</v>
+      </c>
+      <c r="C42" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D42" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E42" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F42" s="94" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="168"/>
+      <c r="B43" s="57" t="s">
         <v>139</v>
       </c>
-      <c r="C36" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="D36" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="E36" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F36" s="107" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="177" t="s">
-        <v>50</v>
-      </c>
-      <c r="B37" s="70" t="s">
+      <c r="C43" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D43" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E43" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F43" s="94" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="168"/>
+      <c r="B44" s="57" t="s">
         <v>140</v>
       </c>
-      <c r="C37" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="D37" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="E37" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F37" s="107" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="178"/>
-      <c r="B38" s="70" t="s">
+      <c r="C44" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D44" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E44" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F44" s="94" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="168"/>
+      <c r="B45" s="57" t="s">
         <v>141</v>
       </c>
-      <c r="C38" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="D38" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="E38" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F38" s="107" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="178"/>
-      <c r="B39" s="70" t="s">
-        <v>197</v>
-      </c>
-      <c r="C39" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="D39" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="E39" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F39" s="107" t="s">
+      <c r="C45" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D45" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E45" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F45" s="94" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="168"/>
+      <c r="B46" s="57" t="s">
+        <v>142</v>
+      </c>
+      <c r="C46" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D46" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E46" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F46" s="94" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="168"/>
+      <c r="B47" s="57" t="s">
+        <v>143</v>
+      </c>
+      <c r="C47" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D47" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E47" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F47" s="94" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="168"/>
+      <c r="B48" s="57" t="s">
+        <v>144</v>
+      </c>
+      <c r="C48" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D48" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E48" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F48" s="94" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="168"/>
+      <c r="B49" s="57" t="s">
+        <v>145</v>
+      </c>
+      <c r="C49" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D49" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E49" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F49" s="94" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="168"/>
+      <c r="B50" s="57" t="s">
+        <v>146</v>
+      </c>
+      <c r="C50" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D50" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E50" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F50" s="94" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="169"/>
+      <c r="B51" s="57" t="s">
+        <v>147</v>
+      </c>
+      <c r="C51" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D51" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E51" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F51" s="94" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="157" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" s="57" t="s">
+        <v>148</v>
+      </c>
+      <c r="C52" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="D52" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="E52" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F52" s="94" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="178"/>
-      <c r="B40" s="70" t="s">
-        <v>142</v>
-      </c>
-      <c r="C40" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="D40" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="E40" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F40" s="107" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="178"/>
-      <c r="B41" s="70" t="s">
-        <v>129</v>
-      </c>
-      <c r="C41" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="D41" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="E41" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F41" s="107" t="s">
+    <row r="53" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="158"/>
+      <c r="B53" s="57" t="s">
+        <v>149</v>
+      </c>
+      <c r="C53" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="D53" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="E53" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F53" s="94" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="159"/>
+      <c r="B54" s="57" t="s">
+        <v>246</v>
+      </c>
+      <c r="C54" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="D54" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="E54" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F54" s="94" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="164" t="s">
+        <v>52</v>
+      </c>
+      <c r="B55" s="57" t="s">
+        <v>150</v>
+      </c>
+      <c r="C55" s="95" t="s">
+        <v>230</v>
+      </c>
+      <c r="D55" s="95" t="s">
+        <v>230</v>
+      </c>
+      <c r="E55" s="95" t="s">
+        <v>230</v>
+      </c>
+      <c r="F55" s="46" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="178"/>
-      <c r="B42" s="70" t="s">
-        <v>130</v>
-      </c>
-      <c r="C42" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="D42" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="E42" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F42" s="107" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="178"/>
-      <c r="B43" s="70" t="s">
-        <v>143</v>
-      </c>
-      <c r="C43" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="D43" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="E43" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F43" s="107" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="178"/>
-      <c r="B44" s="70" t="s">
-        <v>144</v>
-      </c>
-      <c r="C44" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="D44" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="E44" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F44" s="107" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="178"/>
-      <c r="B45" s="70" t="s">
-        <v>145</v>
-      </c>
-      <c r="C45" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="D45" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="E45" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F45" s="107" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="178"/>
-      <c r="B46" s="70" t="s">
-        <v>146</v>
-      </c>
-      <c r="C46" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="D46" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="E46" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F46" s="107" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="178"/>
-      <c r="B47" s="70" t="s">
-        <v>147</v>
-      </c>
-      <c r="C47" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="D47" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="E47" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F47" s="107" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="178"/>
-      <c r="B48" s="70" t="s">
-        <v>148</v>
-      </c>
-      <c r="C48" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="D48" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="E48" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F48" s="107" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="178"/>
-      <c r="B49" s="70" t="s">
-        <v>149</v>
-      </c>
-      <c r="C49" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="D49" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="E49" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F49" s="107" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="178"/>
-      <c r="B50" s="70" t="s">
-        <v>150</v>
-      </c>
-      <c r="C50" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="D50" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="E50" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F50" s="107" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="179"/>
-      <c r="B51" s="70" t="s">
+    <row r="56" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="165"/>
+      <c r="B56" s="57" t="s">
         <v>151</v>
       </c>
-      <c r="C51" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="D51" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="E51" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F51" s="107" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="167" t="s">
-        <v>59</v>
-      </c>
-      <c r="B52" s="70" t="s">
+      <c r="C56" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="D56" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="E56" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F56" s="46" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="166"/>
+      <c r="B57" s="57" t="s">
         <v>152</v>
       </c>
-      <c r="C52" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="D52" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="E52" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F52" s="107" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="168"/>
-      <c r="B53" s="70" t="s">
+      <c r="C57" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="D57" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="E57" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F57" s="46" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="160" t="s">
+        <v>55</v>
+      </c>
+      <c r="B58" s="57" t="s">
         <v>153</v>
       </c>
-      <c r="C53" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="D53" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="E53" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F53" s="107" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="169"/>
-      <c r="B54" s="70" t="s">
-        <v>250</v>
-      </c>
-      <c r="C54" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="D54" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="E54" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F54" s="107" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="174" t="s">
-        <v>52</v>
-      </c>
-      <c r="B55" s="70" t="s">
+      <c r="C58" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="D58" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="E58" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F58" s="46" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="160"/>
+      <c r="B59" s="57" t="s">
         <v>154</v>
       </c>
-      <c r="C55" s="108" t="s">
-        <v>234</v>
-      </c>
-      <c r="D55" s="108" t="s">
-        <v>234</v>
-      </c>
-      <c r="E55" s="108" t="s">
-        <v>234</v>
-      </c>
-      <c r="F55" s="46" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="175"/>
-      <c r="B56" s="70" t="s">
+      <c r="C59" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="D59" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="E59" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F59" s="46" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="149" t="s">
+        <v>62</v>
+      </c>
+      <c r="B60" s="45" t="s">
         <v>155</v>
       </c>
-      <c r="C56" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="D56" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="E56" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F56" s="46" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="176"/>
-      <c r="B57" s="70" t="s">
+      <c r="C60" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="D60" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="E60" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="F60" s="46" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="149"/>
+      <c r="B61" s="45" t="s">
         <v>156</v>
       </c>
-      <c r="C57" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="D57" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="E57" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F57" s="46" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="170" t="s">
-        <v>55</v>
-      </c>
-      <c r="B58" s="70" t="s">
-        <v>157</v>
-      </c>
-      <c r="C58" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="D58" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="E58" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F58" s="46" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="170"/>
-      <c r="B59" s="70" t="s">
-        <v>158</v>
-      </c>
-      <c r="C59" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="D59" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="E59" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F59" s="46" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="129" t="s">
-        <v>62</v>
-      </c>
-      <c r="B60" s="45" t="s">
-        <v>159</v>
-      </c>
-      <c r="C60" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="D60" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="E60" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="F60" s="46" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="129"/>
-      <c r="B61" s="45" t="s">
-        <v>160</v>
-      </c>
-      <c r="C61" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="D61" s="106" t="s">
-        <v>234</v>
-      </c>
-      <c r="E61" s="106" t="s">
-        <v>234</v>
+      <c r="C61" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="D61" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="E61" s="93" t="s">
+        <v>230</v>
       </c>
       <c r="F61" s="46" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -4898,7 +4866,7 @@
     <mergeCell ref="A55:A57"/>
     <mergeCell ref="A37:A51"/>
   </mergeCells>
-  <phoneticPr fontId="20" type="noConversion"/>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -4921,48 +4889,48 @@
   <sheetData>
     <row r="1" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="40" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="41" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="42" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="42" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="42" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="139" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="127" t="s">
+      <c r="B6" s="151" t="s">
         <v>106</v>
       </c>
-      <c r="B6" s="161" t="s">
+      <c r="C6" s="119" t="s">
         <v>107</v>
       </c>
-      <c r="C6" s="142" t="s">
-        <v>108</v>
-      </c>
-      <c r="D6" s="143"/>
-      <c r="E6" s="143"/>
-      <c r="F6" s="161" t="s">
-        <v>162</v>
+      <c r="D6" s="120"/>
+      <c r="E6" s="120"/>
+      <c r="F6" s="151" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="162"/>
-      <c r="B7" s="180"/>
+      <c r="A7" s="152"/>
+      <c r="B7" s="170"/>
       <c r="C7" s="43" t="s">
         <v>36</v>
       </c>
@@ -4972,190 +4940,190 @@
       <c r="E7" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="F7" s="181"/>
+      <c r="F7" s="171"/>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="177" t="s">
+      <c r="A8" s="167" t="s">
+        <v>159</v>
+      </c>
+      <c r="B8" s="57" t="s">
+        <v>160</v>
+      </c>
+      <c r="C8" s="98" t="s">
+        <v>229</v>
+      </c>
+      <c r="D8" s="99" t="s">
+        <v>229</v>
+      </c>
+      <c r="E8" s="99" t="s">
+        <v>243</v>
+      </c>
+      <c r="F8" s="100" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="168"/>
+      <c r="B9" s="57" t="s">
+        <v>191</v>
+      </c>
+      <c r="C9" s="101" t="s">
+        <v>231</v>
+      </c>
+      <c r="D9" s="101" t="s">
+        <v>231</v>
+      </c>
+      <c r="E9" s="101" t="s">
+        <v>231</v>
+      </c>
+      <c r="F9" s="102" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="168"/>
+      <c r="B10" s="57" t="s">
+        <v>161</v>
+      </c>
+      <c r="C10" s="101" t="s">
+        <v>231</v>
+      </c>
+      <c r="D10" s="101" t="s">
+        <v>231</v>
+      </c>
+      <c r="E10" s="101" t="s">
+        <v>231</v>
+      </c>
+      <c r="F10" s="102" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="168"/>
+      <c r="B11" s="47" t="s">
+        <v>162</v>
+      </c>
+      <c r="C11" s="103" t="s">
+        <v>263</v>
+      </c>
+      <c r="D11" s="103" t="s">
+        <v>263</v>
+      </c>
+      <c r="E11" s="101" t="s">
+        <v>230</v>
+      </c>
+      <c r="F11" s="53" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="168"/>
+      <c r="B12" s="44" t="s">
         <v>163</v>
       </c>
-      <c r="B8" s="70" t="s">
+      <c r="C12" s="103" t="s">
+        <v>264</v>
+      </c>
+      <c r="D12" s="103" t="s">
+        <v>264</v>
+      </c>
+      <c r="E12" s="101" t="s">
+        <v>230</v>
+      </c>
+      <c r="F12" s="53" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="168"/>
+      <c r="B13" s="47" t="s">
         <v>164</v>
       </c>
-      <c r="C8" s="111" t="s">
-        <v>233</v>
-      </c>
-      <c r="D8" s="112" t="s">
-        <v>233</v>
-      </c>
-      <c r="E8" s="112" t="s">
-        <v>247</v>
-      </c>
-      <c r="F8" s="113" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="178"/>
-      <c r="B9" s="70" t="s">
-        <v>195</v>
-      </c>
-      <c r="C9" s="114" t="s">
-        <v>235</v>
-      </c>
-      <c r="D9" s="114" t="s">
-        <v>235</v>
-      </c>
-      <c r="E9" s="114" t="s">
-        <v>235</v>
-      </c>
-      <c r="F9" s="115" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="178"/>
-      <c r="B10" s="70" t="s">
+      <c r="C13" s="103" t="s">
+        <v>265</v>
+      </c>
+      <c r="D13" s="103" t="s">
+        <v>265</v>
+      </c>
+      <c r="E13" s="101" t="s">
+        <v>230</v>
+      </c>
+      <c r="F13" s="53" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="168"/>
+      <c r="B14" s="45" t="s">
         <v>165</v>
       </c>
-      <c r="C10" s="114" t="s">
-        <v>235</v>
-      </c>
-      <c r="D10" s="114" t="s">
-        <v>235</v>
-      </c>
-      <c r="E10" s="114" t="s">
-        <v>235</v>
-      </c>
-      <c r="F10" s="115" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="178"/>
-      <c r="B11" s="49" t="s">
+      <c r="C14" s="103" t="s">
+        <v>230</v>
+      </c>
+      <c r="D14" s="103" t="s">
+        <v>230</v>
+      </c>
+      <c r="E14" s="101" t="s">
+        <v>230</v>
+      </c>
+      <c r="F14" s="53" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="168"/>
+      <c r="B15" s="47" t="s">
         <v>166</v>
       </c>
-      <c r="C11" s="116" t="s">
-        <v>267</v>
-      </c>
-      <c r="D11" s="116" t="s">
-        <v>267</v>
-      </c>
-      <c r="E11" s="114" t="s">
-        <v>234</v>
-      </c>
-      <c r="F11" s="60" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="178"/>
-      <c r="B12" s="44" t="s">
+      <c r="C15" s="103" t="s">
+        <v>230</v>
+      </c>
+      <c r="D15" s="103" t="s">
+        <v>230</v>
+      </c>
+      <c r="E15" s="101" t="s">
+        <v>230</v>
+      </c>
+      <c r="F15" s="53" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="169"/>
+      <c r="B16" s="47" t="s">
         <v>167</v>
       </c>
-      <c r="C12" s="116" t="s">
-        <v>268</v>
-      </c>
-      <c r="D12" s="116" t="s">
-        <v>268</v>
-      </c>
-      <c r="E12" s="114" t="s">
-        <v>234</v>
-      </c>
-      <c r="F12" s="60" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="178"/>
-      <c r="B13" s="49" t="s">
-        <v>168</v>
-      </c>
-      <c r="C13" s="116" t="s">
-        <v>269</v>
-      </c>
-      <c r="D13" s="116" t="s">
-        <v>269</v>
-      </c>
-      <c r="E13" s="114" t="s">
-        <v>234</v>
-      </c>
-      <c r="F13" s="60" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="178"/>
-      <c r="B14" s="45" t="s">
-        <v>169</v>
-      </c>
-      <c r="C14" s="116" t="s">
-        <v>234</v>
-      </c>
-      <c r="D14" s="116" t="s">
-        <v>234</v>
-      </c>
-      <c r="E14" s="114" t="s">
-        <v>234</v>
-      </c>
-      <c r="F14" s="60" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="178"/>
-      <c r="B15" s="49" t="s">
-        <v>170</v>
-      </c>
-      <c r="C15" s="116" t="s">
-        <v>234</v>
-      </c>
-      <c r="D15" s="116" t="s">
-        <v>234</v>
-      </c>
-      <c r="E15" s="114" t="s">
-        <v>234</v>
-      </c>
-      <c r="F15" s="60" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="179"/>
-      <c r="B16" s="49" t="s">
-        <v>171</v>
-      </c>
-      <c r="C16" s="116" t="s">
-        <v>234</v>
-      </c>
-      <c r="D16" s="116" t="s">
-        <v>234</v>
-      </c>
-      <c r="E16" s="114" t="s">
-        <v>234</v>
-      </c>
-      <c r="F16" s="60" t="s">
-        <v>274</v>
+      <c r="C16" s="103" t="s">
+        <v>230</v>
+      </c>
+      <c r="D16" s="103" t="s">
+        <v>230</v>
+      </c>
+      <c r="E16" s="101" t="s">
+        <v>230</v>
+      </c>
+      <c r="F16" s="53" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="34" t="s">
-        <v>172</v>
-      </c>
-      <c r="B17" s="51" t="s">
-        <v>173</v>
-      </c>
-      <c r="C17" s="117" t="s">
-        <v>270</v>
-      </c>
-      <c r="D17" s="117" t="s">
-        <v>270</v>
-      </c>
-      <c r="E17" s="114" t="s">
-        <v>234</v>
-      </c>
-      <c r="F17" s="52" t="s">
-        <v>275</v>
+        <v>168</v>
+      </c>
+      <c r="B17" s="48" t="s">
+        <v>169</v>
+      </c>
+      <c r="C17" s="104" t="s">
+        <v>266</v>
+      </c>
+      <c r="D17" s="104" t="s">
+        <v>266</v>
+      </c>
+      <c r="E17" s="101" t="s">
+        <v>230</v>
+      </c>
+      <c r="F17" s="49" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.2"/>
@@ -5181,7 +5149,7 @@
     <mergeCell ref="F6:F7"/>
     <mergeCell ref="A8:A16"/>
   </mergeCells>
-  <phoneticPr fontId="20" type="noConversion"/>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -5204,54 +5172,54 @@
   <sheetData>
     <row r="1" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="40" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B1" s="41"/>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="41" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="42" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="42" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="42" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="50" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="139" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="53" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="127" t="s">
-        <v>106</v>
-      </c>
-      <c r="B7" s="161" t="s">
-        <v>176</v>
-      </c>
-      <c r="C7" s="142" t="s">
-        <v>108</v>
-      </c>
-      <c r="D7" s="143"/>
-      <c r="E7" s="143"/>
-      <c r="F7" s="161" t="s">
-        <v>162</v>
+      <c r="B7" s="151" t="s">
+        <v>172</v>
+      </c>
+      <c r="C7" s="119" t="s">
+        <v>107</v>
+      </c>
+      <c r="D7" s="120"/>
+      <c r="E7" s="120"/>
+      <c r="F7" s="151" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="162"/>
-      <c r="B8" s="180"/>
+      <c r="A8" s="152"/>
+      <c r="B8" s="170"/>
       <c r="C8" s="43" t="s">
         <v>36</v>
       </c>
@@ -5261,147 +5229,235 @@
       <c r="E8" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="181"/>
-    </row>
-    <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="129" t="s">
+      <c r="F8" s="171"/>
+    </row>
+    <row r="9" spans="1:6" ht="30" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="149" t="s">
+        <v>173</v>
+      </c>
+      <c r="B9" s="44" t="s">
+        <v>174</v>
+      </c>
+      <c r="C9" s="98" t="s">
+        <v>264</v>
+      </c>
+      <c r="D9" s="99" t="s">
+        <v>266</v>
+      </c>
+      <c r="E9" s="99" t="s">
+        <v>272</v>
+      </c>
+      <c r="F9" s="105" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="30" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="149"/>
+      <c r="B10" s="45" t="s">
+        <v>175</v>
+      </c>
+      <c r="C10" s="98" t="s">
+        <v>264</v>
+      </c>
+      <c r="D10" s="99" t="s">
+        <v>266</v>
+      </c>
+      <c r="E10" s="99" t="s">
+        <v>272</v>
+      </c>
+      <c r="F10" s="53" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="30" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="149"/>
+      <c r="B11" s="45" t="s">
+        <v>176</v>
+      </c>
+      <c r="C11" s="98" t="s">
+        <v>264</v>
+      </c>
+      <c r="D11" s="99" t="s">
+        <v>266</v>
+      </c>
+      <c r="E11" s="99" t="s">
+        <v>272</v>
+      </c>
+      <c r="F11" s="53" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="30" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="149"/>
+      <c r="B12" s="45" t="s">
         <v>177</v>
       </c>
-      <c r="B9" s="44" t="s">
+      <c r="C12" s="98" t="s">
+        <v>264</v>
+      </c>
+      <c r="D12" s="99" t="s">
+        <v>266</v>
+      </c>
+      <c r="E12" s="99" t="s">
+        <v>272</v>
+      </c>
+      <c r="F12" s="53" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="167" t="s">
         <v>178</v>
       </c>
-      <c r="C9" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="D9" s="48" t="s">
-        <v>111</v>
-      </c>
-      <c r="E9" s="48" t="s">
-        <v>112</v>
-      </c>
-      <c r="F9" s="54" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="129"/>
-      <c r="B10" s="45" t="s">
+      <c r="B13" s="45" t="s">
         <v>179</v>
       </c>
-      <c r="C10" s="55"/>
-      <c r="D10" s="56"/>
-      <c r="E10" s="56"/>
-      <c r="F10" s="57"/>
-    </row>
-    <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="129"/>
-      <c r="B11" s="45" t="s">
+      <c r="C13" s="98" t="s">
+        <v>264</v>
+      </c>
+      <c r="D13" s="99" t="s">
+        <v>266</v>
+      </c>
+      <c r="E13" s="99" t="s">
+        <v>272</v>
+      </c>
+      <c r="F13" s="53" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="30" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="169"/>
+      <c r="B14" s="51" t="s">
         <v>180</v>
       </c>
-      <c r="C11" s="55"/>
-      <c r="D11" s="56"/>
-      <c r="E11" s="56"/>
-      <c r="F11" s="50"/>
-    </row>
-    <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="129"/>
-      <c r="B12" s="45" t="s">
+      <c r="C14" s="98" t="s">
+        <v>285</v>
+      </c>
+      <c r="D14" s="99" t="s">
+        <v>286</v>
+      </c>
+      <c r="E14" s="99" t="s">
+        <v>272</v>
+      </c>
+      <c r="F14" s="53" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="30" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="167" t="s">
         <v>181</v>
       </c>
-      <c r="C12" s="55"/>
-      <c r="D12" s="56"/>
-      <c r="E12" s="56"/>
-      <c r="F12" s="50"/>
-    </row>
-    <row r="13" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="177" t="s">
+      <c r="B15" s="45" t="s">
         <v>182</v>
       </c>
-      <c r="B13" s="45" t="s">
+      <c r="C15" s="98" t="s">
+        <v>264</v>
+      </c>
+      <c r="D15" s="99" t="s">
+        <v>266</v>
+      </c>
+      <c r="E15" s="99" t="s">
+        <v>272</v>
+      </c>
+      <c r="F15" s="53" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="30" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="168"/>
+      <c r="B16" s="45" t="s">
         <v>183</v>
       </c>
-      <c r="C13" s="55"/>
-      <c r="D13" s="56"/>
-      <c r="E13" s="56"/>
-      <c r="F13" s="50"/>
-    </row>
-    <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="179"/>
-      <c r="B14" s="58" t="s">
+      <c r="C16" s="98" t="s">
+        <v>264</v>
+      </c>
+      <c r="D16" s="99" t="s">
+        <v>266</v>
+      </c>
+      <c r="E16" s="99" t="s">
+        <v>272</v>
+      </c>
+      <c r="F16" s="53" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="30" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="169"/>
+      <c r="B17" s="45" t="s">
         <v>184</v>
       </c>
-      <c r="C14" s="59"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="60"/>
-    </row>
-    <row r="15" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="177" t="s">
+      <c r="C17" s="98" t="s">
+        <v>264</v>
+      </c>
+      <c r="D17" s="99" t="s">
+        <v>266</v>
+      </c>
+      <c r="E17" s="99" t="s">
+        <v>272</v>
+      </c>
+      <c r="F17" s="106" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="30" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="34" t="s">
         <v>185</v>
       </c>
-      <c r="B15" s="45" t="s">
+      <c r="B18" s="45" t="s">
         <v>186</v>
       </c>
-      <c r="C15" s="55"/>
-      <c r="D15" s="56"/>
-      <c r="E15" s="56"/>
-      <c r="F15" s="50"/>
-    </row>
-    <row r="16" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="178"/>
-      <c r="B16" s="45" t="s">
+      <c r="C18" s="98" t="s">
+        <v>264</v>
+      </c>
+      <c r="D18" s="99" t="s">
+        <v>266</v>
+      </c>
+      <c r="E18" s="99" t="s">
+        <v>272</v>
+      </c>
+      <c r="F18" s="106" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="157" t="s">
         <v>187</v>
       </c>
-      <c r="C16" s="55"/>
-      <c r="D16" s="56"/>
-      <c r="E16" s="56"/>
-      <c r="F16" s="50"/>
-    </row>
-    <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="179"/>
-      <c r="B17" s="45" t="s">
+      <c r="B19" s="45" t="s">
         <v>188</v>
       </c>
-      <c r="C17" s="61"/>
-      <c r="D17" s="62"/>
-      <c r="E17" s="62"/>
-      <c r="F17" s="63"/>
-    </row>
-    <row r="18" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="34" t="s">
+      <c r="C19" s="98" t="s">
+        <v>264</v>
+      </c>
+      <c r="D19" s="99" t="s">
+        <v>266</v>
+      </c>
+      <c r="E19" s="99" t="s">
+        <v>272</v>
+      </c>
+      <c r="F19" s="106" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="30" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="159"/>
+      <c r="B20" s="45" t="s">
         <v>189</v>
       </c>
-      <c r="B18" s="45" t="s">
-        <v>190</v>
-      </c>
-      <c r="C18" s="61"/>
-      <c r="D18" s="62"/>
-      <c r="E18" s="62"/>
-      <c r="F18" s="63"/>
-    </row>
-    <row r="19" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="167" t="s">
-        <v>191</v>
-      </c>
-      <c r="B19" s="45" t="s">
-        <v>192</v>
-      </c>
-      <c r="C19" s="61"/>
-      <c r="D19" s="62"/>
-      <c r="E19" s="62"/>
-      <c r="F19" s="63"/>
-    </row>
-    <row r="20" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="169"/>
-      <c r="B20" s="45" t="s">
-        <v>193</v>
-      </c>
-      <c r="C20" s="64"/>
-      <c r="D20" s="65"/>
-      <c r="E20" s="65"/>
-      <c r="F20" s="66"/>
-    </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="C20" s="98" t="s">
+        <v>264</v>
+      </c>
+      <c r="D20" s="99" t="s">
+        <v>266</v>
+      </c>
+      <c r="E20" s="99" t="s">
+        <v>272</v>
+      </c>
+      <c r="F20" s="107" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.2"/>
     <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -5426,7 +5482,7 @@
     <mergeCell ref="C7:E7"/>
     <mergeCell ref="A13:A14"/>
   </mergeCells>
-  <phoneticPr fontId="20" type="noConversion"/>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
